--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -10,32 +10,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤情鉴定" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤残情况" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外伤与退变对照" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转院报销" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'伤情鉴定'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤残情况'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'费用台账'!$A$2:$H$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'费用台账'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'72小时待办'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'沟通口径卡'!$A$1:$B$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'沟通口径卡'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'责任与程序'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'责任与程序'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'录音来源'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'录音来源'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -704,13 +707,95 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>附录：轻弦办公椅上海园区快闪（同批 8 月 15 日录音，与事故无关）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>产品：轻弦人体工学椅；供方称字节、大疆、小米等有总部集采。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>合作：物业大堂快闪 + 企业内购；单椅成交返佣 100–200 元；可用椅子抵场地费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>渠道：杨浦滨江、徐汇滨江；合作方有闵行森马、杨浦科创等园区资源。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>下一步：供方发资料；合作方下下周回沪后选 1–2 个园区试点。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -895,11 +980,23 @@
       </c>
       <c r="C14" s="4" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>不要把人社局电话咨询当成交通事故评残。人社局管工伤、残疾人证等另一套制度；本案评残走司法鉴定</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
-  <mergeCells count="6">
+  <autoFilter ref="A1:C15"/>
+  <mergeCells count="7">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B14:C14"/>
@@ -1073,6 +1170,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>人已到人民医院，齐鲁出院未办。二甲能不能报，保险公司说了算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>目前事实</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>怎么处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>当前卡住</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 中午：伤者已同意并搬到市北区人民医院，齐鲁出院单未办，二甲因此无法办理入院。这是当前第一优先，比谈残级、谈责任都急。</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>当天办齐鲁出院结算，再办人民医院入院</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>结算规则</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>跨院必须先在上一院结算，才能办下一院入院。出院部和科室权责分离，只找出院部催科室留床没有用。证件、押金票据带到齐鲁办理窗口（通话提到 11 楼）。</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>带齐证件和押金票，出院部和科室分开催</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>朋友怎么说</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>8 月 17 日 12:57 咨询：对方称公立二甲及以上一般在商业保险报销范围内，民营和一级社区医院通常不认。这只是朋友经验，对方自己只是骨裂、没住院，不能当保单条款。</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>仅参考，不能当保单</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>家属口径</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>家属会后口径正确：二甲能不能报，由保险公司确定。保险说二甲不行就不能继续住；保险说可以，再安心住；保险要求回三甲，由保险医务部门对接医院。</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>采用这一条</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>交警口径</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>交警工作口径是去三甲。对市北区人民医院无法书面保证一定能理赔，但同路段类似骨折有在该院治疗且未因医院级别拒赔的先例。</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>留痕，不把交警口头当保险确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>今天目标</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>今天先把出院/入院手续打通，避免治疗空窗。住哪一级以保险公司书面或通话确认为准，不以朋友一句「公立二甲都报」为准。</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>手续打通 + 保险确认二甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>明确不做</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>不要装病拒绝出院、不要「出院再以新患者入院」去绕床位考核——这是咨询人给的偏门办法，不做。
+不要给交警或医院换号、代扮身份。对方要谁的电话，就给谁的电话。
+不要把人社局「伤残补助」当成交通事故评残入口。那是另一套制度。
+不要为了留在三甲去谈红包或所谓保护费。</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>装病、绕考核、代扮、人社局评残，全部停</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1384,19 +1651,29 @@
       <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>专业转运/救护车</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr"/>
+          <t>转院救护车</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>160</v>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>未发生或待核</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>已付待核</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>家属</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>待贴</t>
@@ -1405,7 +1682,7 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>责任方承担，不自掏不留票</t>
+          <t>预估150，实收160，必须发票</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1553,7 +1830,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本周只办治疗不断档、证据固定、保险进群。不谈残级。</t>
+          <t>今天先打通出院入院，并向保险公司确认二甲。不谈残级。</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1872,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>下载并保存三份 CT 报告 PDF/截图、影像入口、检查号</t>
+          <t>当天办齐鲁出院结算（带齐证件、押金票），再办人民医院入院</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>这是目前最硬的伤情证据</t>
+          <t>人已到二甲但无入院身份，治疗空窗最危险</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1615,17 +1892,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>家属</t>
+          <t>家属+交警</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>向齐鲁医院要：入院记录、手术记录、术后医嘱、费用明细和发票</t>
+          <t>向交警要美团/平台保险公司电话，问清：市北区人民医院费用能否理赔</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>理赔和日后评残都靠病历，不靠口述</t>
+          <t>二甲能不能住，保险公司说了算，朋友说了不算</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1645,12 +1922,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>先完成当前医院结算规则要求的手续，避免「未结算无法入院」空窗</t>
+          <t>下载并保存三份 CT 报告、齐鲁手术记录、费用明细和发票</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>伤者术后不能断治疗</t>
+          <t>这是目前最硬的伤情和花费证据</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1670,12 +1947,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>医院资质一事公对公：交警电话可给赛主任，但口径必须是交警自己的原话，不代扮交警</t>
+          <t>医院资质公对公留痕：交警电话可给赛主任，口径必须是交警原话</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>二甲理赔风险要留痕，不能靠口头「应该没问题」</t>
+          <t>不代扮交警，不换号</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1749,13 +2026,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1885,7 +2162,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>患者是交通事故伤者，后续理赔对医院级别敏感，优先三甲连续治疗。</t>
+          <t>患者是交通事故伤者。请先协助办完齐鲁出院结算，再办人民医院入院，不要人在床上没有住院号。</t>
         </is>
       </c>
     </row>
@@ -1897,7 +2174,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运。</t>
+          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运、开具发票。</t>
         </is>
       </c>
     </row>
@@ -1916,36 +2193,36 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>绝对不要说</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>不要再说「对方全责」——交警视频已经排除。</t>
+          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院后续费用，是否都属于可赔医院。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>绝对不要说</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>不要对外说「已经几级伤残」。</t>
+          <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>绝对不要说</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
+          <t>请告知理赔需要的材料清单、是否必须先有责任认定书才能垫付医疗费。</t>
         </is>
       </c>
     </row>
@@ -1957,7 +2234,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+          <t>不要再说「对方全责」——交警视频已经排除。</t>
         </is>
       </c>
     </row>
@@ -1969,12 +2246,72 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>不要对外说「已经几级伤残」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>不要无发票的现金开支事后补口。</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -1983,7 +2320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2167,13 +2504,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2185,7 +2522,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>得到大脑 10 份录音。与 CT 冲突的以 CT 为准。</t>
+          <t>得到大脑 11 份录音。与 CT 冲突的以 CT 为准；二甲报销以保险公司为准。</t>
         </is>
       </c>
     </row>
@@ -2431,94 +2768,34 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>伤者转院报销问题咨询</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>46:00</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>人已到人民医院、齐鲁未出院；朋友称公立二甲可报，会后改为以保险公司确认为准</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>附录：轻弦办公椅上海园区快闪（同批 8 月 15 日录音，与事故无关）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>产品：轻弦人体工学椅；供方称字节、大疆、小米等有总部集采。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>合作：物业大堂快闪 + 企业内购；单椅成交返佣 100–200 元；可用椅子抵场地费。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>渠道：杨浦滨江、徐汇滨江；合作方有闵行森马、杨浦科创等园区资源。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>下一步：供方发资料；合作方下下周回沪后选 1–2 个园区试点。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B6"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -25,13 +25,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1181,7 +1181,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人已到人民医院，齐鲁出院未办。二甲能不能报，保险公司说了算。</t>
+          <t>人已到人民医院，齐鲁出院未办。医保能报 ≠ 美团险能报。</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>当前卡住</t>
@@ -1219,113 +1219,183 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>怎么转出来的</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>院方口径是联合体、同一家医院、不影响质量。昨天沟通过两次没转成，父亲好说话才同意，今天上午才搬走。主治态度强硬，青岛这边没有上海那种关系。</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>父亲好说话才同意；主治强硬，不指望找关系留床</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>不是康复期</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>不要把现在当成康复期。8 月 15 日术后 CT 仍写软组织肿胀、内外固定刚做完，到 17 日只过了两天。朋友说「已经康复期就别折腾」与影像时间轴不符。</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>术后两天，软组织仍肿，不能按康复期处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>两条报销</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>报销要分两条，不能混：① 医保：公立二甲通常能走医保结算；② 美团平台险/交通事故赔偿：认不认这家医院，必须问美团保险，朋友一句「公立二甲都报」覆盖不了这一条。</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>医保和美团险分开问</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>找哪家保险</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>咨询人说「认定单上一定有保险公司电话」。本案对方是外卖电动车，没有交强险、商业三者险。认定书上未必印着人保/平安。要找的是美团平台险，问交警、骑手、站点，不要只在认定单上找传统车险公司。</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>问交警/骑手/站点要美团平台险，不在认定单上找交强险</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>结算规则</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>跨院必须先在上一院结算，才能办下一院入院。出院部和科室权责分离，只找出院部催科室留床没有用。证件、押金票据带到齐鲁办理窗口（通话提到 11 楼）。</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>带齐证件和押金票，出院部和科室分开催</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>带齐证件和押金票</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>朋友怎么说</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>8 月 17 日 12:57 咨询：对方称公立二甲及以上一般在商业保险报销范围内，民营和一级社区医院通常不认。这只是朋友经验，对方自己只是骨裂、没住院，不能当保单条款。</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>8 月 17 日 12:57 咨询：对方称公立二甲及以上一般在保险报销范围内，民营和一级社区医院通常不认；还让把医院全称发给他核对。对方自己只是骨裂、没住院，不能当美团保单条款。</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>仅参考，不能当保单</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>家属口径</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>家属会后口径正确：二甲能不能报，由保险公司确定。保险说二甲不行就不能继续住；保险说可以，再安心住；保险要求回三甲，由保险医务部门对接医院。</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>采用这一条</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>交警口径</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>交警工作口径是去三甲。对市北区人民医院无法书面保证一定能理赔，但同路段类似骨折有在该院治疗且未因医院级别拒赔的先例。</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>留痕，不把交警口头当保险确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>家属会后口径正确：二甲能不能报，由保险公司确定。保险说二甲不行就不能继续住；保险说可以，再安心住；保险要求回三甲，由保险医务部门对接医院。向保险报医院全称：市北区人民医院（抚顺路院区）。</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>采用；向保险报医院全称</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>别的三甲</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>不要另找别的三甲碰运气。齐鲁是山大直属附属医院，床位本就紧；全国三甲都考床位周转，病情未到「必须三甲抢救」时，别人也难收长期占床。</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>不另找山大体系外三甲碰运气</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>今天目标</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>今天先把出院/入院手续打通，避免治疗空窗。住哪一级以保险公司书面或通话确认为准，不以朋友一句「公立二甲都报」为准。</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>手续打通 + 保险确认二甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>今天先把出院/入院手续打通，避免治疗空窗。住哪一级以美团保险公司书面或通话确认为准，不以朋友一句「公立二甲都报」为准。</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>手续打通 + 美团险确认二甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>明确不做</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>不要装病拒绝出院、不要「出院再以新患者入院」去绕床位考核——这是咨询人给的偏门办法，不做。
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>不要装病拒绝出院、不要「出院再以新患者入院」去绕床位考核——主治强硬、本地没关系，这条更走不通。
 不要给交警或医院换号、代扮身份。对方要谁的电话，就给谁的电话。
 不要把人社局「伤残补助」当成交通事故评残入口。那是另一套制度。
-不要为了留在三甲去谈红包或所谓保护费。</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>装病、绕考核、代扮、人社局评残，全部停</t>
+不要为了留在三甲去谈红包或所谓保护费。
+不要把医保能报，说成美团险一定能报。
+不要对保险或交警说「已经是康复期」。</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>装病、绕考核、代扮、人社局评残、混医保，全部停</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9"/>
+  <autoFilter ref="A1:C13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -1892,17 +1962,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>家属+交警</t>
+          <t>家属+交警+骑手</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>向交警要美团/平台保险公司电话，问清：市北区人民医院费用能否理赔</t>
+          <t>要美团平台险电话（不是交强险公司），报医院全称问：市北区人民医院费用能否理赔</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>二甲能不能住，保险公司说了算，朋友说了不算</t>
+          <t>外卖电动车没有交强险；认定单上未必有人保/平安</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2032,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2198,7 +2268,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院后续费用，是否都属于可赔医院。</t>
+          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院（抚顺路院区）后续费用，是否都属于可赔医院。请用医院全称核对。</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2376,36 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>不要把医保结算说成美团险已经确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>不要说伤者已经进入康复期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B23"/>
+  <autoFilter ref="A1:B25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -2786,7 +2880,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>人已到人民医院、齐鲁未出院；朋友称公立二甲可报，会后改为以保险公司确认为准</t>
+          <t>同场录音补充：医保≠美团险；术后两天不是康复期；认定单上未必有传统车险公司</t>
         </is>
       </c>
     </row>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="52" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>当前卡住</t>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>怎么转出来的</t>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>不是康复期</t>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>两条报销</t>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>找哪家保险</t>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>结算规则</t>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>朋友怎么说</t>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>家属口径</t>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>别的三甲</t>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>今天目标</t>
@@ -1372,30 +1372,158 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>明确不做</t>
+          <t>医院怎么选</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>不要装病拒绝出院、不要「出院再以新患者入院」去绕床位考核——主治强硬、本地没关系，这条更走不通。
-不要给交警或医院换号、代扮身份。对方要谁的电话，就给谁的电话。
-不要把人社局「伤残补助」当成交通事故评残入口。那是另一套制度。
-不要为了留在三甲去谈红包或所谓保护费。
-不要把医保能报，说成美团险一定能报。
-不要对保险或交警说「已经是康复期」。</t>
+          <t>不建议去转其他三甲。也不建议在入院未办成、美团险未确认前，把留在市北区人民医院当成既定方案。首选能回齐鲁就回齐鲁。</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>装病、绕考核、代扮、人社局评残、混医保，全部停</t>
+          <t>不另找三甲；不默认留二甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>首选齐鲁</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>手术在齐鲁手足与显微重建外科做的，内外固定还在，术后只有两天，软组织仍肿。齐鲁是三甲，交警默认三甲，病历连续，出现伤口或外固定问题能找原手术组。这是医疗和理赔都最稳的选择。</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>赛主任态度强硬，床位周转考核，明确不愿让交通事故患者长期占床。昨天谈了两次才转出，父亲已经同意搬走。没有关系硬闯，成功率不高。所以是合法问一次能不能收回，不是闹回去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>不另找三甲</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>其他三甲同样考床位周转，不收刚做完手术、还要住一个月的占床。新医院不掌握术中情况，外固定再搬一次有风险，又要重新结算入院。只有齐鲁拒收且美团险不认人民医院时，才由保险协调下一家三甲。</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>只有保险书面指定才动</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>不默认留二甲</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>市北区人民医院是公立二甲、联合体，环境清静，赛主任称可每周查房。但现在入院手续都没办成；美团险还没确认认不认；术后两天不是康复期。医保能报不能代替美团险确认。</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>先问美团险，先办入院号</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>今天先做</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>办齐鲁出院结算，结束没有住院号的空窗。同时问赛主任：术后两天、外固定在、交警要求三甲、二甲还办不了入院，能否收回本院。同时问美团险：市北区人民医院（抚顺路院区）后续费用认不认。</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>齐鲁能收回</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>回齐鲁。这是首选。不要再转第三次。</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁明确收不回，美团险确认人民医院可赔</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>暂留市北区人民医院。留痕：保险认这家医院；赛主任每周查房谁来、哪天来。发热、伤口渗液、外固定松动、剧痛、脚趾发绀，立刻回三甲急诊。</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>美团险不认人民医院</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>不要继续住。请保险医务部门对接齐鲁或指定三甲。家属不自己满城找床。</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁拒收且保险也不认二甲、保险又协调不出三甲</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>这才考虑其他三甲，而且要保险书面指定，不要自己去碰。</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>对赛主任原话</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>赛主任，患者8月15日刚做完右踝内外固定，今天二甲入院手续还办不成。交警口径是交通事故尽量三甲。术后只有两天，不是康复期。请协助：要么尽快办完出院让二甲能入院，要么收回齐鲁本院连续治疗。我们按医院规则走，不闹、不装病。</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>不闹、不装病</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -1942,12 +2070,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>当天办齐鲁出院结算（带齐证件、押金票），再办人民医院入院</t>
+          <t>当天办齐鲁出院结算；同时问赛主任能否收回本院（术后两天、外固定、交警要三甲）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>人已到二甲但无入院身份，治疗空窗最危险</t>
+          <t>空窗最危险；能回齐鲁就回，问一次是正当的</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2232,7 +2360,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>患者是交通事故伤者。请先协助办完齐鲁出院结算，再办人民医院入院，不要人在床上没有住院号。</t>
+          <t>请先协助办完齐鲁出院结算。患者术后只有两天、外固定还在、二甲入院还办不成。请明确：能否收回齐鲁本院连续治疗；若不能，请马上把出院办完，避免没有住院号。</t>
         </is>
       </c>
     </row>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -29,9 +29,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
@@ -1818,7 +1818,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>不确定项，必须合同+发票</t>
+          <t>24小时一对一，合同+发票；按责比例报，不是全额。家属自己陪护无票</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2209,8 +2209,33 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>家属</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>护士站请本院合作一对一 24 小时护工（合同+发票）；胡继刚办完住院号、拉群、约交警后回上海上班</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>现在不能自理，12 小时夜里没人；家属自己陪护的工资报不了，护工发票才能按责报护理费</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2230,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2427,12 +2452,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>绝对不要说</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>不要再说「对方全责」——交警视频已经排除。</t>
+          <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2469,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>不要对外说「已经几级伤残」。</t>
+          <t>不要再说「对方全责」——交警视频已经排除。</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2481,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
+          <t>不要对外说「已经几级伤残」。</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2493,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2505,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>不要无发票的现金开支事后补口。</t>
+          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2517,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
+          <t>不要无发票的现金开支事后补口。</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2529,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>不要把医保结算说成美团险已经确认。</t>
+          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2541,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>不要说伤者已经进入康复期。</t>
+          <t>不要把医保结算说成美团险已经确认。</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2553,24 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>不要说伤者已经进入康复期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B25"/>
+  <autoFilter ref="A1:B26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -29,11 +29,11 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'录音来源'!$A$1:$D$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'录音来源'!$1:$2</definedName>
@@ -2015,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2210,32 +2210,57 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" t="n">
+      <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>护士站请本院合作一对一 24 小时护工（合同+发票）；胡继刚办完住院号、拉群、约交警后回上海上班</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>现在不能自理，12 小时夜里没人；家属自己陪护的工资报不了，护工发票才能按责报护理费</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>家属+岳父</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>内部固定刘孝春角色：车是他的、活是他的、无劳动合同；先收微信转账、现场证人，不发律师函，不签与刘了结</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>他可能分担己方份额和车主过错，但不能替美团骑手补差额，两笔账不能混</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2255,7 +2280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2569,8 +2594,32 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>不要把刘孝春写成工伤单位去人社局；退休未签合同，工伤这条很窄。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B26"/>
+  <autoFilter ref="A1:B28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -2585,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2625,7 +2674,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>青岛市北区红枫路汽车市场外抚顺路（正规市政道路，批发市场附近）</t>
+          <t>干活在青岛市市北区抚顺路批发市场一带；碰撞按交警案卷，材料仍写抚顺路市政道路（红枫路汽车市场外），不要写成纯市场内部事故。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2642,7 +2691,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>伤者骑三轮车准备掉头，后方美团二轮电动车碰撞，三轮侧翻。交警称视频能看清过程。</t>
+          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车准备掉头，后方美团二轮电动车碰撞，三轮侧翻。交警称视频能看清过程。</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -2659,7 +2708,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（批发市场自制内部牌，家属记得 2588，交警不认可）；转向灯失灵，掉头未有效提示后方；掉头动作违规：先向右靠再大弧度左拐，易误导后方</t>
+          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧、转向灯失灵，掉头未有效提示后方；掉头动作违规：先向右靠再大弧度左拐，易误导后方</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2753,8 +2802,59 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>刘孝春身份</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，当时没有签劳动合同。</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>车主/接受劳务方，不是工伤单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>不替美团补</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>刘孝春没有法定义务承担「美团小姑娘责任范围内赔不够、她本人又没钱」的那一块。那是骑手和美团平台险的债，不能让老板去替她补。</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>骑手责任范围内的缺口仍找平台险和骑手</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>可主张己方份</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>认定书扣掉的己方份额（同等大约 50%，次责大约 30%）以及因车主过错、提供不合格车辆产生的相应责任，可以向刘孝春主张分担。这是「三轮这一方内部怎么分」，不是「替美团赔剩余」。</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>无牌+灯坏交人使用，车主有过错线索；先留证据不发函</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:C13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
@@ -35,10 +36,12 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'录音来源'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'录音来源'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -164,6 +167,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -713,6 +717,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>得到大脑 11 份录音。与 CT 冲突的以 CT 为准；二甲报销以保险公司为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>本表如何使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>伤势与理赔情况讨论</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>早期口述伤情与费用，须用 CT 校正</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>轻弦办公椅园区快闪洽谈</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>同批录音，与事故无关，见附录</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>美团医疗赔偿家属协商</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>催款、转院、发票、伤残鉴定流程的家属共识</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>与骑手赔偿责任通话</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>骑手要等认定书；家属要求拉群</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>医院转院结算流程</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>必须先结算再入院；三级诊疗解释</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>红枫路交警沟通</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>责任范围、简易/一般、保险、医院级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>交警补充：赔偿职权边界</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>02:23</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>交警不下赔偿金额；评残后再谈残</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>交警：二甲入院与执行风险</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>三甲默认、二甲不确定、骑手偿付弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>与赛主任转院沟通</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>联合体二甲惯例；交警电话公对公</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>转院问题内部/律师讨论</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>38:06</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>必须回三甲的策略讨论；责任预判须服从交警视频</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>伤者转院报销问题咨询</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>46:00</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>同场录音补充：医保≠美团险；术后两天不是康复期；认定单上未必有传统车险公司</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2869,290 +3169,530 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>得到大脑 11 份录音。与 CT 冲突的以 CT 为准；二甲报销以保险公司为准。</t>
+          <t>30%是己方缺口不是刘的固定比例。未结工钱100%由刘付，其余进总损失后再切。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>现在能否主张</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>时长</t>
+          <t>计算口径</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>本表如何使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>刘孝春怎么担</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>不要搞错</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>未结工钱（欠薪）</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>伤势与理赔情况讨论</t>
+          <t>可以现在就要</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>按实际未付工钱，8/15 口述约 5000 元，须微信或证人核。</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>早期口述伤情与费用，须用 CT 校正</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>100% 由刘孝春付。这是欠薪，不乘 30%，不和事故赔偿冲抵。</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>不要拿欠薪去抵医疗费后说事故两清。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>医疗费</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>轻弦办公椅园区快闪洽谈</t>
+          <t>有票就进台账</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>住院、手术、检查、药品、后续门诊，发票减医保已报（按保险和法院口径）。</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>同批录音，与事故无关，见附录</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>进入 L，刘分担缺口 G 中与其过错相当的部分。</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>美团 70% 仍找平台险，不让刘替骑手出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>后续治疗费</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>美团医疗赔偿家属协商</t>
+          <t>评残前先记账，取内固定后再结</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>医嘱或鉴定意见载明的二次手术、拆外固定、康复必要费用。</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>催款、转院、发票、伤残鉴定流程的家属共识</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>同上，进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>不要现在把尚未发生的二次手术一次性包死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>护理费（陪护费）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>与骑手赔偿责任通话</t>
+          <t>应当主张</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03:19</t>
+          <t>医院合作一对一 24 小时合同+发票；出院后仍不能自理的，按医嘱天数和当地护工价。青岛约 300–350 元/天。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>骑手要等认定书；家属要求拉群</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>应当分担缺口里的护理费，不是把全部护工费甩给刘。家属自己陪护无票的，很难按上海工资认。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>一对多、微信私拉、无发票，刘和保险都可以不认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>住院伙食补助费</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>医院转院结算流程</t>
+          <t>应当主张</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>住院天数 × 青岛国家机关工作人员出差伙食补助标准。</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>必须先结算再入院；三级诊疗解释</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>没有住院天数就不要编。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>营养费</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>红枫路交警沟通</t>
+          <t>有医嘱再主张</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>医嘱写加强营养或鉴定支持的天数 × 当地标准。</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>责任范围、简易/一般、保险、医院级别</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>没有医嘱不要按骨折吓人程度口头加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>交通费</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>交警补充：赔偿职权边界</t>
+          <t>有票就主张</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>02:23</t>
+          <t>救护车 160 元；家属合理往返（胡继刚上海—青岛按必要次数）。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>交警不下赔偿金额；评残后再谈残</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>旅游、探亲顺便的车票不要混进去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>住宿费</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>交警：二甲入院与执行风险</t>
+          <t>有票且必要才主张</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>外地家属因处理事故、陪护产生的合理住宿。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>三甲默认、二甲不确定、骑手偿付弱</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>长期住酒店替代护工，容易被砍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>误工费（伤者本人）</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>与赛主任转院沟通</t>
+          <t>能证明收入才主张</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>03:27</t>
+          <t>只算胡某。64 岁已退休，须证明实际在给刘干活有收入（微信、证人、市场行情）。误工天数看出院医嘱或鉴定休息期。</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>联合体二甲惯例；交警电话公对公</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>误工费若成立，刘分担的是缺口里这一项，不是按儿子上海工资赔，也不是把胡某后半生工资全包。</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>证明不了实际收入，误工费可能为 0。胡继刚的工资不是误工费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>残疾赔偿金</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>转院问题内部/律师讨论</t>
+          <t>评残后才有</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>38:06</t>
+          <t>青岛口径内部用 71703 元/年 × 16 年 × 残级系数（十级 0.1，九级 0.2）。</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>必须回三甲的策略讨论；责任预判须服从交警视频</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>评残后进入 L，刘仍只切 30% 缺口里与其过错相当的部分。</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>现在不要对外报残级，也不要让刘现在按十级锁死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>残疾辅助器具费</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>伤者转院报销问题咨询</t>
+          <t>有医嘱或鉴定再主张</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>46:00</t>
+          <t>拐杖、轮椅等必要器具。</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>同场录音补充：医保≠美团险；术后两天不是康复期；认定单上未必有传统车险公司</t>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>高消费器材没有医嘱不要报。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>被扶养人生活费</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>评残后看有没有法定被扶养人</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>须评残且有胡某依法扶养、无劳动能力又无生活来源的人。成年儿子胡继刚一般不算。</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>若成立，进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>不要把全家生活费写成被扶养人生活费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>精神损害抚慰金</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>评残或起诉时主张</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>按伤情和当地法院尺度。美团平台险常常不赔这一项。</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>保险不赔的部分，可向有过错的侵权人主张；刘作为车主/接受劳务过错方，可能分担己方缺口里的相应部分，不是替骑手把精神抚慰金全包。</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>不要以为刘必须把保险除外的精神抚慰金全部补上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>鉴定费</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>评残时发生</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>道路交通事故伤残鉴定费，发票。</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口；有的判决由败诉方负担，以判决为准。</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>不要网上计算器代替鉴定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>个人物品损失</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>有凭证再主张</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>衣服、眼镜、手机等因事故损坏。</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>三轮车是刘的，车损不是胡某向刘索赔的项目；车损由刘自行向美团侧按责主张。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>不应承担</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>美团骑手责任范围内（约 70%）赔不够的部分——仍是骑手和平台险的债。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>胡继刚回上海少拿的工资、请护工之外自己陪护的「误工」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>无合同、无发票的现金护工，以及一对多护工。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>跟骨骨刺、退变等与本次事故无关的治疗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>把刘孝春的三轮车损算成胡某的损失向刘要钱。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>工伤待遇、社保补缴——退休未签合同，这条基本走不通。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>现在就按十级、九级向刘要残疾赔偿金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>总损失 L（下列可计入项目之和）→ 美团/平台险先赔约 70%L → 己方缺口 G≈30%L → 刘孝春赔 G×其过错系数 k，胡某自负 G×(1−k)。k 不是 100%，也不要对外报一个数；无牌+灯坏交人上路、当天派活，主张时把 k 往高处谈，但不能写成刘把 30% 全部包圆。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <autoFilter ref="A1:E28"/>
+  <mergeCells count="9">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -16,8 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
@@ -38,10 +39,12 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'录音来源'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待补充信息'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'待补充信息'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -717,6 +720,336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>这条消息若没有新事实，按本表补。补齐后发文字即可写入材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>已经掌握</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>还缺什么</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>找谁要</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>缓急</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>事故现场</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>周五出事、抚顺路市政道路、先右靠再大弧度左拐、灯不亮、后方碰撞、三轮侧翻</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>具体钟点、天气、车道数、两车颜色品牌、货是否在车上、精确撞击部位、是否戴头盔</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>交警监控原视频 / 陈师傅</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>车速与距离</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>后方车距不足、骑手视野更好</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>两车大概时速、跟车距离（米）、有没有刹车痕迹</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>监控逐帧 / 认定书</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>刘孝春</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>碰撞瞬间他在不在现场；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏；现场证人姓名电话</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>刘孝春、市场同事</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>胡某驾驶资格</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>交警认定三轮属机动车</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>有没有对应准驾资格。只内部掌握，不要对外主动提，一般程序才可能查</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>家属内部核对</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>急（内部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>医院手续</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁手术 8/15，人已到人民医院</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁出院结算单、人民医院住院号、赛主任能否收回的答复</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>出院处 / 赛主任</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>护工</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>现在按不能自理、应请 24 小时一对一</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>合同、发票、护理记录、日单价、开始日期</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>护士站本院合作公司</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>美团保险</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>电动车无交强险，赔付靠平台险按责</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>站点 + 平台险进微信群</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>交警程序</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>监控已调、排除全责、两车已扣</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>面谈时间、简易还是一般、认定书原件复印件</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>陈师傅</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>费用发票</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>口述 3.5 万与 7 万冲突；救护车 160；雇主垫 2 万待核</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>医院窗口</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>美团骑手</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>女骑手、二轮、配偶也送外卖、两子、偿付弱</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>姓名、电话、站点名称、平台险对接人进群</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>骑手 / 交警</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1007,7 +1340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'伤情鉴定'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
@@ -33,15 +33,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待补充信息'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'待补充信息'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'录音来源'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'附录轻弦洽谈'!$1:$2</definedName>
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -733,7 +733,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>这条消息若没有新事实，按本表补。补齐后发文字即可写入材料。</t>
+          <t>8/19 补充后仍缺的事实。没有就不要编进 3D 或对外口径。3D 视频留作待用。</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>周五出事、抚顺路市政道路、先右靠再大弧度左拐、灯不亮、后方碰撞、三轮侧翻</t>
+          <t>周五出事、批发市场外市政道路护栏开口附近、先右借道再大弧度左拐、灯不亮、后方碰撞、三轮侧翻</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>具体钟点、天气、车道数、两车颜色品牌、货是否在车上、精确撞击部位、是否戴头盔</t>
+          <t>具体钟点、天气、车道数、两车颜色品牌、货是否在车上、精确撞击部位、是否戴头盔；交警原视频（3D 复原待用，本次不重做）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -794,22 +794,22 @@
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>车速与距离</t>
+          <t>护栏与地点</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>后方车距不足、骑手视野更好</t>
+          <t>掉头因护栏开口先借道；地点有红枫路汽车市场、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能同一片</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>两车大概时速、跟车距离（米）、有没有刹车痕迹</t>
+          <t>护栏开口照片、现场示意图；交警文书上的正式路名</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>监控逐帧 / 认定书</t>
+          <t>胡继刚现场补拍 / 认定书</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -821,22 +821,22 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>刘孝春</t>
+          <t>姓名核对</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏</t>
+          <t>伤者胡某、对接人胡继刚、用工老板口述刘孝春；转写有刘小春、胡志远</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>碰撞瞬间他在不在现场；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏；现场证人姓名电话</t>
+          <t>身份证、病历首页、微信实名，对外材料只用证件姓名</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>刘孝春、市场同事</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -848,49 +848,49 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>胡某驾驶资格</t>
+          <t>车速与距离</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>交警认定三轮属机动车</t>
+          <t>后方车距不足、骑手视野更好</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>有没有对应准驾资格。只内部掌握，不要对外主动提，一般程序才可能查</t>
+          <t>两车大概时速、跟车距离（米）、有没有刹车痕迹</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>家属内部核对</t>
+          <t>监控逐帧 / 认定书</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>急（内部）</t>
+          <t>中</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>医院手续</t>
+          <t>刘孝春</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>齐鲁手术 8/15，人已到人民医院</t>
+          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>齐鲁出院结算单、人民医院住院号、赛主任能否收回的答复</t>
+          <t>碰撞瞬间他在不在现场；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏；现场证人姓名电话</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>出院处 / 赛主任</t>
+          <t>刘孝春、市场同事</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -902,49 +902,49 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>护工</t>
+          <t>胡某驾驶资格</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>现在按不能自理、应请 24 小时一对一</t>
+          <t>交警认定三轮属机动车</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>合同、发票、护理记录、日单价、开始日期</t>
+          <t>有没有对应准驾资格。只内部掌握，不要对外主动提，一般程序才可能查</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>护士站本院合作公司</t>
+          <t>家属内部核对</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>急</t>
+          <t>急（内部）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>美团保险</t>
+          <t>医院手续</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>电动车无交强险，赔付靠平台险按责</t>
+          <t>齐鲁手术 8/15，人已到人民医院</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认</t>
+          <t>齐鲁出院结算单、人民医院住院号、赛主任能否收回的答复</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>站点 + 平台险进微信群</t>
+          <t>出院处 / 赛主任</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -956,22 +956,22 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>交警程序</t>
+          <t>护工</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>监控已调、排除全责、两车已扣</t>
+          <t>现在按不能自理、应请 24 小时一对一</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>面谈时间、简易还是一般、认定书原件复印件</t>
+          <t>合同、发票、护理记录、日单价、开始日期</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>陈师傅</t>
+          <t>护士站本院合作公司</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -983,22 +983,22 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>费用发票</t>
+          <t>美团保险</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>口述 3.5 万与 7 万冲突；救护车 160；雇主垫 2 万待核</t>
+          <t>电动车无交强险，赔付靠平台险按责</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核</t>
+          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>医院窗口</t>
+          <t>站点 + 平台险进微信群</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1010,32 +1010,86 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>交警程序</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>监控已调、排除全责、两车已扣</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>面谈时间、简易还是一般、认定书原件复印件</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>陈师傅</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>费用发票</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>口述 3.5 万与 7 万冲突；救护车 160；雇主垫 2 万待核</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>医院窗口</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>美团骑手</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>女骑手、二轮、配偶也送外卖、两子、偿付弱</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>姓名、电话、站点名称、平台险对接人进群</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>骑手 / 交警</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>急</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1050,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1062,7 +1116,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>得到大脑 11 份录音。与 CT 冲突的以 CT 为准；二甲报销以保险公司为准。</t>
+          <t>得到大脑转写 14 条索引。与 CT 冲突的以 CT 为准。录音≠认定书。3D 视频留作待用。</t>
         </is>
       </c>
     </row>
@@ -1330,8 +1384,74 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>哈尔滨路叉车交通事故责任沟通讨论</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>转写</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>护栏开口借道、车辆归刘孝春、70%/30% 是内部设想不是认定书。标题「叉车」是转写错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>工伤交通事故赔偿案件的律师选择与费用沟通</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>转写</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>收费方式讨论；九级、25–30 万是另一案例，不能套本案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>17份得到大脑材料整理底稿</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>书面</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>录音转写≠病历/认定书/保单。地点别称、姓名转写、护栏开口口径见该整理稿。3D 视频本次不重做。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D13"/>
+  <autoFilter ref="A1:D16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -1646,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1787,8 +1907,93 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>录音把车说成「叉车」</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>涉事是货运三轮，交警口头认定为机动车。不要对外说叉车。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>地点有红枫路、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等说法</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>可能指同一片批发市场外道路。对外写：批发市场外市政道路护栏开口附近，地址以交警文书为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>录音写成「刘小春」</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>家属口述用工老板为刘孝春。转写可能同音错字，以身份证、微信实名为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>录音写成「胡志远」</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>家属对接人是儿子胡继刚。伤者写胡某。姓名以身份证、病历首页为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>律师沟通里出现九级伤残、赔偿 25 万至 30 万</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>那是另一个参考案例或收费举例，不能当本案结论。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A1:C13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -2913,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2959,7 +3164,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>请协助本周见到骑手，并请对方当场确认美团/保险公司联系人。</t>
+          <t>掉头先右再左，是因为护栏开口借道，不是随意变道。请结合监控和现场勘查写进认定书。我们仍不争全责。</t>
         </is>
       </c>
     </row>
@@ -2971,7 +3176,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>就医医院请书面或通话留痕：默认三甲；若暂留二甲，是否影响保险审核。</t>
+          <t>请协助本周见到骑手，并请对方当场确认美团/保险公司联系人。</t>
         </is>
       </c>
     </row>
@@ -2983,19 +3188,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>简易程序可以谈，但要先问清保险能否在该责任比例下正常赔。</t>
+          <t>就医医院请书面或通话留痕：默认三甲；若暂留二甲，是否影响保险审核。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>对骑手/平台</t>
+          <t>对交警</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>先看病、先垫付已发生医疗费，态度摆正，拉群不打游击电话。</t>
+          <t>简易程序可以谈，但要先问清保险能否在该责任比例下正常赔。</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3212,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>请平台和保险进群。个人经济情况理解，但规则归规则。</t>
+          <t>先看病、先垫付已发生医疗费，态度摆正，拉群不打游击电话。</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3224,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>不接受「等认定书之前什么都不做」。认定书管责任，不管伤者今天能不能住院。</t>
+          <t>请平台和保险进群。个人经济情况理解，但规则归规则。</t>
         </is>
       </c>
     </row>
@@ -3031,19 +3236,19 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
+          <t>不接受「等认定书之前什么都不做」。认定书管责任，不管伤者今天能不能住院。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>对医院</t>
+          <t>对骑手/平台</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>请先协助办完齐鲁出院结算。患者术后只有两天、外固定还在、二甲入院还办不成。请明确：能否收回齐鲁本院连续治疗；若不能，请马上把出院办完，避免没有住院号。</t>
+          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3260,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运、开具发票。</t>
+          <t>请先协助办完齐鲁出院结算。患者术后只有两天、外固定还在、二甲入院还办不成。请明确：能否收回齐鲁本院连续治疗；若不能，请马上把出院办完，避免没有住院号。</t>
         </is>
       </c>
     </row>
@@ -3067,19 +3272,19 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>请出具诊断证明、手术名称、预计住院和康复周期。</t>
+          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运、开具发票。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>对保险公司</t>
+          <t>对医院</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院（抚顺路院区）后续费用，是否都属于可赔医院。请用医院全称核对。</t>
+          <t>请出具诊断证明、手术名称、预计住院和康复周期。</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3296,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
+          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院（抚顺路院区）后续费用，是否都属于可赔医院。请用医院全称核对。</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3308,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>请告知理赔需要的材料清单、是否必须先有责任认定书才能垫付医疗费。</t>
+          <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
         </is>
       </c>
     </row>
@@ -3115,19 +3320,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
+          <t>请告知理赔需要的材料清单、是否必须先有责任认定书才能垫付医疗费。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>绝对不要说</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>不要再说「对方全责」——交警视频已经排除。</t>
+          <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3344,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>不要对外说「已经几级伤残」。</t>
+          <t>不要再说「对方全责」——交警视频已经排除。</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3356,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
+          <t>不要对外说「已经几级伤残」。</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3368,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3380,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>不要无发票的现金开支事后补口。</t>
+          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3392,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
+          <t>不要无发票的现金开支事后补口。</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3404,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>不要把医保结算说成美团险已经确认。</t>
+          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3416,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>不要说伤者已经进入康复期。</t>
+          <t>不要把医保结算说成美团险已经确认。</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3428,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
+          <t>不要说伤者已经进入康复期。</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3440,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3452,60 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>不要把刘孝春写成工伤单位去人社局；退休未签合同，工伤这条很窄。</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>不要对外说叉车。涉事是货运三轮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>不要把「骑手 70%、用工方 30%」说成交警认定——那是内部讨论。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B28"/>
+  <autoFilter ref="A1:B32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -3307,7 +3560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>干活在青岛市市北区抚顺路批发市场一带；碰撞按交警案卷，材料仍写抚顺路市政道路（红枫路汽车市场外），不要写成纯市场内部事故。</t>
+          <t>干活在青岛市市北区批发市场一带。碰撞在市场外市政道路护栏开口附近。录音里还有红枫路汽车市场、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能指同一片，地址以交警文书为准。不要写成纯市场内部事故，也不要写成叉车事故。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3324,7 +3577,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车准备掉头，后方美团二轮电动车碰撞，三轮侧翻。交警称视频能看清过程。</t>
+          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。因护栏开口和道路结构，掉头时先向右借道调整位置，再大弧度向左拐。后方美团二轮电动车碰撞，三轮侧翻压伤右下肢。交警称视频能看清过程。护栏开口可以解释动作来源，但不能据此争全责。</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3341,7 +3594,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧、转向灯失灵，掉头未有效提示后方；掉头动作违规：先向右靠再大弧度左拐，易误导后方</t>
+          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧、转向灯失灵，掉头未有效提示后方；掉头动作：先向右靠再大弧度左拐。8 月 18 日家属解释是护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3375,7 +3628,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>监控可排除任何一方全责。可能结果只有两种：双方同等责任；或三轮次责、外卖主责。交警称无论简易、一般程序还是法院，看了视频都不会超出该范围。</t>
+          <t>监控可排除任何一方全责。可能结果只有两种：双方同等责任；或三轮次责、外卖主责。交警称无论简易、一般程序还是法院，看了视频都不会超出该范围。8 月 18 日内部说的「骑手 70%、用工方 30%」是讨论意见，不是认定书。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'伤情鉴定'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
@@ -41,7 +41,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'待补充信息'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'录音来源'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'附录轻弦洽谈'!$1:$2</definedName>
@@ -772,7 +772,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>周五出事、批发市场外市政道路护栏开口附近、先右借道再大弧度左拐、灯不亮、后方碰撞、三轮侧翻</t>
+          <t>周五出事；卸完第一趟回装第二趟；哈尔滨路水果市场 1 号门斜坡护栏开口（还没到红绿灯）；双方口述都往上走；先借道再掉头；灯不亮；后方碰撞；踏板压右脚</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>掉头因护栏开口先借道；地点有红枫路汽车市场、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能同一片</t>
+          <t>1 号门斜坡护栏开口借道；地点还有红枫路、福生、服装批发市场斜坡红绿灯等叫法</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>伤者胡某、对接人胡继刚、用工老板口述刘孝春；转写有刘小春、胡志远</t>
+          <t>对接人胡继刚；齐鲁转写 33 床胡志远；用工老板口述刘孝春（转写刘小春）；有人问过孙总被否认</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏</t>
+          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏、口述大灯也坏；8/15 口述雇主在现场</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>碰撞瞬间他在不在现场；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏；现场证人姓名电话</t>
+          <t>碰撞瞬间在不在现场的证人；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>齐鲁手术 8/15，人已到人民医院</t>
+          <t>齐鲁手术 8/15；人已到人民医院；戴老师补打 33 床出院记录、不用单独盖章；结余一楼原路退</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>齐鲁出院结算单、人民医院住院号、赛主任能否收回的答复</t>
+          <t>补打件是否已交人民医院并办成住院号；王主任对「报不了就回齐鲁」的落实</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>出院处 / 赛主任</t>
+          <t>出院处 / 王主任 / 人民医院入院处</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>电动车无交强险，赔付靠平台险按责</t>
+          <t>电动车无交强险；8/17 骑手称已打客服未回信；约定加 1866 开头微信</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认</t>
+          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认的正式答复</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>站点 + 平台险进微信群</t>
+          <t>骑手微信 + 站点 + 平台险进群</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核</t>
+          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核。记录 13 的 8000 元不是本案</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>医院窗口</t>
+          <t>医院一楼收费窗口</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1104,19 +1104,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>得到大脑转写 14 条索引。与 CT 冲突的以 CT 为准。录音≠认定书。3D 视频留作待用。</t>
+          <t>得到大脑转写 18 条索引。与 CT 冲突的以 CT 为准。录音≠认定书。3D 视频留作待用。</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>伤势与理赔情况讨论</t>
+          <t>1｜伤势与理赔情况讨论</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>早期口述伤情与费用，须用 CT 校正</t>
+          <t>第一趟卸完回装第二趟、踏板压右脚、雇主口述在场。伤情/全责/出院须用 CT 和 8/17 交警校正</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>轻弦办公椅园区快闪洽谈</t>
+          <t>2｜轻弦办公椅园区快闪洽谈</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>同批录音，与事故无关，见附录</t>
+          <t>与事故无关，见附录</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>美团医疗赔偿家属协商</t>
+          <t>3｜美团医疗赔偿家属协商</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>与骑手赔偿责任通话</t>
+          <t>4｜与骑手赔偿责任通话</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>骑手要等认定书；家属要求拉群</t>
+          <t>骑手要等认定书；家属要求拉群、不满未探望</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>医院转院结算流程</t>
+          <t>5｜医院转院结算流程</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>红枫路交警沟通</t>
+          <t>6｜红枫路交警沟通</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>交警补充：赔偿职权边界</t>
+          <t>7｜交警补充：赔偿职权边界</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>交警：二甲入院与执行风险</t>
+          <t>8｜交警：二甲入院与执行风险</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>与赛主任转院沟通</t>
+          <t>9｜转院问题内部/律师讨论</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>03:27</t>
+          <t>38:06</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>联合体二甲惯例；交警电话公对公</t>
+          <t>必须回三甲的策略讨论；责任预判须服从交警视频</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>转院问题内部/律师讨论</t>
+          <t>10｜与赛主任转院沟通</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>38:06</t>
+          <t>03:27</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>必须回三甲的策略讨论；责任预判须服从交警视频</t>
+          <t>联合体二甲惯例；交警电话公对公</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>伤者转院报销问题咨询</t>
+          <t>11｜伤者转院报销问题咨询</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1380,78 +1380,166 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>同场录音补充：医保≠美团险；术后两天不是康复期；认定单上未必有传统车险公司</t>
+          <t>医保≠美团险；术后两天不是康复期；认定单上未必有传统车险公司</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>哈尔滨路叉车交通事故责任沟通讨论</t>
+          <t>12｜请对方联系保险公司</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>转写</t>
+          <t>00:39</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>护栏开口借道、车辆归刘孝春、70%/30% 是内部设想不是认定书。标题「叉车」是转写错误。</t>
+          <t>让二轮女骑手联系保险；能赔才留人民医院</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>工伤交通事故赔偿案件的律师选择与费用沟通</t>
+          <t>13｜补打出院记录（病区串台）</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>转写</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>收费方式讨论；九级、25–30 万是另一案例，不能套本案。</t>
+          <t>只取 33 床戴老师补打出院记录、不用盖章、一楼原路退。蒋玉年/8000 元不是本案</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>14｜骑手侧保险报销确认</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>骑手称已打客服未回信；加微信 1866；地点有人叫福生批发市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15｜问医院二甲报销与王主任</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>保险说了算；报不了就回齐鲁；王主任落实</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>16｜律师选择与费用（另一案）</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>仅作收费常识。九级、25–30 万、远洋工伤是另一案，不能套本案</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>17｜护栏开口内部讨论</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1 号门斜坡护栏开口、双方上坡、大灯也坏。标题「叉车」和「驾驶人 0 责」不要对外</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>17份得到大脑材料整理底稿</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>书面｜沟通记录合集口径对照</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>书面</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>录音转写≠病历/认定书/保单。地点别称、姓名转写、护栏开口口径见该整理稿。3D 视频本次不重做。</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>17 份原文怎么用、合集目录拆案纠正、新补事实清单</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:D20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -1766,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1988,12 +2076,97 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>那是另一个参考案例或收费举例，不能当本案结论。</t>
+          <t>那是记录 16 的远洋工伤另一案（已评残、拖了近五年），不能当本案结论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>合集目录把 17 份拆成多起车祸/叉车/行人</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>记录 1、3–15、17 是同一起三轮×美团女骑手事故。记录 2 轻弦无关。记录 16 是另一案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>有人问是不是给孙总卸货</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>伤者当场否认，说是给刘孝春干活。不要写成孙总。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>记录 13 出现蒋玉年、陈先建、26 床、8000 元</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>病区串台。本案只取 33 床补打出院记录、一楼原路退费。其他人和其他钱不要进台账。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>8 月 15 日说交警已经定全责</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>8 月 17 日交警看监控排除任何一方全责。早期口述作废。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>通话须改口</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>记录 17 说驾驶人 0 责、刘孝春把 30% 全包</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>内部设想。交警仍可能把无牌、灯坏、掉头记在三轮使用人胡某这一方。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -2048,7 +2221,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 中午：伤者已同意并搬到市北区人民医院，齐鲁出院单未办，二甲因此无法办理入院。这是当前第一优先，比谈残级、谈责任都急。</t>
+          <t>2026-08-17 下午：人已到市北区人民医院。齐鲁 33 床出院记录由戴老师补打，不用单独盖章，交给人民医院办入院。结余去齐鲁一楼收费窗口原路退。骑手称已打保险客服、尚未回信，约定加 1866 开头微信。二甲认不认仍以保险书面/通话为准，医院对接王主任：报不了就回齐鲁。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2908,12 +3081,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>当天办齐鲁出院结算；同时问赛主任能否收回本院（术后两天、外固定、交警要三甲）</t>
+          <t>取齐鲁 33 床补打出院记录交人民医院办住院号；同时去一楼收费窗口办结余原路退；问王主任：保险不认二甲能否收回齐鲁</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>空窗最危险；能回齐鲁就回，问一次是正当的</t>
+          <t>空窗最危险；补打件不用单独盖章；能回齐鲁就回</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2928,17 +3101,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>家属+交警+骑手</t>
+          <t>家属+骑手</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>要美团平台险电话（不是交强险公司），报医院全称问：市北区人民医院费用能否理赔</t>
+          <t>加 1866 开头微信，催保险客服书面答复：市北区人民医院（抚顺路院区）认不认、赔付比例、要不要认定书才能垫</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>外卖电动车没有交强险；认定单上未必有人保/平安</t>
+          <t>骑手 8/17 下午只说打了客服还没回信，不能当成已经确认</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3118,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3164,7 +3337,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>掉头先右再左，是因为护栏开口借道，不是随意变道。请结合监控和现场勘查写进认定书。我们仍不争全责。</t>
+          <t>掉头先右再左，是因为哈尔滨路水果市场 1 号门斜坡护栏开口借道，不是随意变道。双方口述都往上走。请结合监控和现场勘查写进认定书。我们仍不争全责。</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3397,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>请平台和保险进群。个人经济情况理解，但规则归规则。</t>
+          <t>请平台和保险进群。8 月 17 日你说已打客服、加 1866 微信，现在要书面结果：人民医院认不认、赔付比例。</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3433,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>请先协助办完齐鲁出院结算。患者术后只有两天、外固定还在、二甲入院还办不成。请明确：能否收回齐鲁本院连续治疗；若不能，请马上把出院办完，避免没有住院号。</t>
+          <t>请先协助：补打的 33 床出院记录交给人民医院办住院号；结余去一楼收费窗口原路退。若美团险不认二甲，请王主任协助退回齐鲁连续治疗。</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3673,48 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>不要把「骑手 70%、用工方 30%」说成交警认定——那是内部讨论。</t>
+          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>不要写成给孙总干活。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B32"/>
+  <autoFilter ref="A1:B35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -3560,7 +3769,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>干活在青岛市市北区批发市场一带。碰撞在市场外市政道路护栏开口附近。录音里还有红枫路汽车市场、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能指同一片，地址以交警文书为准。不要写成纯市场内部事故，也不要写成叉车事故。</t>
+          <t>干活在青岛市市北区批发市场一带。8 月 18 日口述更细：哈尔滨路水果市场门口、1 号门出口斜坡、护栏开口处，还没到红绿灯大路口。录音里还有红枫路汽车市场、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能指同一片，地址以交警文书为准。不要写成纯市场内部事故，也不要写成叉车事故。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3577,7 +3786,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。因护栏开口和道路结构，掉头时先向右借道调整位置，再大弧度向左拐。后方美团二轮电动车碰撞，三轮侧翻压伤右下肢。交警称视频能看清过程。护栏开口可以解释动作来源，但不能据此争全责。</t>
+          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3594,7 +3803,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧、转向灯失灵，掉头未有效提示后方；掉头动作：先向右靠再大弧度左拐。8 月 18 日家属解释是护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
+          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧：转向灯失灵，8 月 18 日口述大灯也坏，掉头未有效提示后方；掉头动作：先向上/向右借道再大弧度左拐。8 月 18 日家属解释是 1 号门斜坡护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3628,7 +3837,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>监控可排除任何一方全责。可能结果只有两种：双方同等责任；或三轮次责、外卖主责。交警称无论简易、一般程序还是法院，看了视频都不会超出该范围。8 月 18 日内部说的「骑手 70%、用工方 30%」是讨论意见，不是认定书。</t>
+          <t>监控可排除任何一方全责。可能结果只有两种：双方同等责任；或三轮次责、外卖主责。交警称无论简易、一般程序还是法院，看了视频都不会超出该范围。8 月 18 日内部说的「骑手 70%、刘孝春 30%、驾驶人 0 责」是讨论意见，不是认定书。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法律关系提醒" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
@@ -33,18 +34,20 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'待补充信息'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'录音来源'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'法律关系提醒'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'法律关系提醒'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'待补充信息'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'录音来源'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -720,6 +723,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>不必等法院先确认雇佣关系。垫付和欠薪必须写清性质。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>提醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>不必等法院先确认「雇佣/劳务法律关系」才去留证、收垫付、要欠薪。现在就能做。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>工伤已经排除：未签劳动合同，不具备工伤认定条件。不要去人社局。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>雇员受害仍可主张：有乔刘记商贸派活、车是刘的、人在卸货、有工钱或欠薪，即可按民法典 1192、1209 主张。法院以后怎么定性，是起诉时的事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>3 万元现金立刻写收据：垫付医疗费，不是借款，不是一次性了结交通事故，不冲抵欠薪，不代美团赔偿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>未结工钱约 5000 另写一张欠薪确认，不乘责任比例，不和垫付混在一张纸上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>4 万元和 3 万元用发票分清后再对外报一个数。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -772,12 +877,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>周五出事；卸完第一趟回装第二趟；哈尔滨路水果市场 1 号门斜坡护栏开口（还没到红绿灯）；双方口述都往上走；先借道再掉头；灯不亮；后方碰撞；踏板压右脚</t>
+          <t>周五出事；抚顺路批发市场、抚顺路与哈尔滨路交叉口；护栏开口借道；踏板压右脚；灯不亮；后方碰撞</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>具体钟点、天气、车道数、两车颜色品牌、货是否在车上、精确撞击部位、是否戴头盔；交警原视频（3D 复原待用，本次不重做）</t>
+          <t>具体钟点、天气、车道数、两车颜色品牌、货是否在车上、精确撞击部位；交警原视频（3D 待用）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -799,17 +904,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1 号门斜坡护栏开口借道；地点还有红枫路、福生、服装批发市场斜坡红绿灯等叫法</t>
+          <t>家属确认：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口；护栏开口借道</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>护栏开口照片、现场示意图；交警文书上的正式路名</t>
+          <t>认定书正式路名、现场图、护栏开口照片</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>胡继刚现场补拍 / 认定书</t>
+          <t>认定书 / 胡继刚补拍</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -821,22 +926,22 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>姓名核对</t>
+          <t>刘孝春</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>对接人胡继刚；齐鲁转写 33 床胡志远；用工老板口述刘孝春（转写刘小春）；有人问过孙总被否认</t>
+          <t>乔刘记商贸负责人；雇佣无合同；工伤排除；市场内部牌；转向灯坏；已垫付现金 3 万</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>身份证、病历首页、微信实名，对外材料只用证件姓名</t>
+          <t>3 万垫付收据（性质三句话）；欠薪 5000 书面；4 万费用发票分清；营业执照/微信抬头</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>刘孝春</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -848,49 +953,49 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>车速与距离</t>
+          <t>胡某驾驶资格</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>后方车距不足、骑手视野更好</t>
+          <t>家属确认具备驾驶资格证书</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>两车大概时速、跟车距离（米）、有没有刹车痕迹</t>
+          <t>内部留驾驶证复印件。不要主动交给一般程序扩查</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>监控逐帧 / 认定书</t>
+          <t>胡继刚内部</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>已确认</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>刘孝春</t>
+          <t>美团保险</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>车主、派卸货、无劳动合同、市场内部牌约 2588、转向灯坏、口述大灯也坏；8/15 口述雇主在现场</t>
+          <t>平台美团；人民医院可以赔、比例待定；二级以上公立医保范围内用药可以</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>碰撞瞬间在不在现场的证人；微信工钱流水；未结工钱实数；他是否知道没牌和灯坏</t>
+          <t>骑手拉群：保险公司名称、保单号、报案号、限额、书面比例、要不要认定书才能垫</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>刘孝春、市场同事</t>
+          <t>骑手拉群</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -902,49 +1007,49 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>胡某驾驶资格</t>
+          <t>交警程序</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>交警认定三轮属机动车</t>
+          <t>监控已调、排除全责、两车已扣；认定书尚未出具</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>有没有对应准驾资格。只内部掌握，不要对外主动提，一般程序才可能查</t>
+          <t>预计出具时间；律师看完监控再选简易或一般；认定书原件</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>家属内部核对</t>
+          <t>陈师傅 + 律师</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>急（内部）</t>
+          <t>急</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>医院手续</t>
+          <t>费用发票</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>齐鲁手术 8/15；人已到人民医院；戴老师补打 33 床出院记录、不用单独盖章；结余一楼原路退</t>
+          <t>垫付现金 3 万；费用口径确认 4 万；口述 5000 欠薪</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>补打件是否已交人民医院并办成住院号；王主任对「报不了就回齐鲁」的落实</t>
+          <t>发票对账；3 万与 4 万分清；垫付收据；欠薪书面。记录 13 的 8000 元不是本案</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>出院处 / 王主任 / 人民医院入院处</t>
+          <t>医院窗口 + 刘孝春收据</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -956,22 +1061,22 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>护工</t>
+          <t>姓名核对</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>现在按不能自理、应请 24 小时一对一</t>
+          <t>对接人胡继刚；齐鲁转写 33 床胡志远；用工老板口述刘孝春（转写刘小春）；有人问过孙总被否认</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>合同、发票、护理记录、日单价、开始日期</t>
+          <t>身份证、病历首页、微信实名，对外材料只用证件姓名</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>护士站本院合作公司</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -983,49 +1088,49 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>美团保险</t>
+          <t>车速与距离</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>电动车无交强险；8/17 骑手称已打客服未回信；约定加 1866 开头微信</t>
+          <t>后方车距不足、骑手视野更好</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>保单号/工号、限额、医疗是否另封顶、要不要认定书才能垫、人民医院抚顺路院区认不认的正式答复</t>
+          <t>两车大概时速、跟车距离（米）、有没有刹车痕迹</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>骑手微信 + 站点 + 平台险进群</t>
+          <t>监控逐帧 / 认定书</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>急</t>
+          <t>中</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>交警程序</t>
+          <t>医院手续</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>监控已调、排除全责、两车已扣</t>
+          <t>齐鲁手术 8/15；人已到人民医院；保险侧确认二甲可赔、比例待定</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>面谈时间、简易还是一般、认定书原件复印件</t>
+          <t>住院号；书面赔付比例；手术记录和植入物清单（钢钉根数）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>陈师傅</t>
+          <t>入院处 / 保险书面 / 病案室</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1037,22 +1142,22 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>费用发票</t>
+          <t>护工</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>口述 3.5 万与 7 万冲突；救护车 160；雇主垫 2 万待核</t>
+          <t>现在按不能自理、应请 24 小时一对一</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>齐鲁对账单、押金、手术费、药品、救护车发票；两套数用票重核。记录 13 的 8000 元不是本案</t>
+          <t>合同、发票、护理记录、日单价、开始日期</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>医院一楼收费窗口</t>
+          <t>护士站本院合作公司</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1069,17 +1174,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>女骑手、二轮、配偶也送外卖、两子、偿付弱</t>
+          <t>女骑手、美团平台、二轮</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>姓名、电话、站点名称、平台险对接人进群</t>
+          <t>姓名、电话、站点名称；拉群确认保险公司和保单</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骑手 / 交警</t>
+          <t>骑手拉群</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1098,7 +1203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1524,7 +1629,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>书面｜沟通记录合集口径对照</t>
+          <t>书面｜家属确认待确认事项</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1534,7 +1639,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>17 份原文怎么用、合集目录拆案纠正、新补事实清单</t>
+          <t>认定书未出；抚顺路路口；有驾驶证；人民医院可赔比例待定；乔刘记商贸；垫付 3 万；费用口径 4 万；工伤排除；程序由律师定</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2025,7 +2130,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>可能指同一片批发市场外道路。对外写：批发市场外市政道路护栏开口附近，地址以交警文书为准。</t>
+          <t>家属确认：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。对外用这一条，仍以认定书为准。用户一条里写「抚松路」按抚顺路统一。</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2326,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17 下午：人已到市北区人民医院。齐鲁 33 床出院记录由戴老师补打，不用单独盖章，交给人民医院办入院。结余去齐鲁一楼收费窗口原路退。骑手称已打保险客服、尚未回信，约定加 1866 开头微信。二甲认不认仍以保险书面/通话为准，医院对接王主任：报不了就回齐鲁。</t>
+          <t>2026-08-19 家属确认：市北区人民医院费用可以赔，比例待定。口径：二级以上公立医院、医保范围内用药可以。人已到人民医院（公立二甲）。书面比例、保单号、住院号仍要盯。认定书尚未出具。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>当天办齐鲁出院结算，再办人民医院入院</t>
+          <t>要书面比例和住院号；可以暂留人民医院</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2377,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>报销要分两条，不能混：① 医保：公立二甲通常能走医保结算；② 美团平台险/交通事故赔偿：认不认这家医院，必须问美团保险，朋友一句「公立二甲都报」覆盖不了这一条。</t>
+          <t>报销仍分两条：① 医保：公立二甲通常能结算；② 美团平台险：家属确认可以赔、比例待定，二级以上公立医院医保范围内用药可以。比例和限额仍要书面，不能当全额。</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2340,7 +2445,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>家属会后口径正确：二甲能不能报，由保险公司确定。保险说二甲不行就不能继续住；保险说可以，再安心住；保险要求回三甲，由保险医务部门对接医院。向保险报医院全称：市北区人民医院（抚顺路院区）。</t>
+          <t>家属确认人民医院可以赔、比例待定。向保险继续要书面：赔付比例、保单号、限额、要不要认定书才能垫付。医院全称：市北区人民医院（抚顺路院区）。</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2374,7 +2479,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>今天先把出院/入院手续打通，避免治疗空窗。住哪一级以美团保险公司书面或通话确认为准，不以朋友一句「公立二甲都报」为准。</t>
+          <t>住院号办成；保险书面比例拿到手。可以暂留人民医院，但比例未定不要当全额报销。</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2391,7 +2496,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>不建议去转其他三甲。也不建议在入院未办成、美团险未确认前，把留在市北区人民医院当成既定方案。首选能回齐鲁就回齐鲁。</t>
+          <t>家属确认人民医院（公立二甲）费用可以赔，比例待定。二级以上公立医院、医保范围内用药可以。不必再为「二甲能不能报」来回搬人。比例书面未到之前，不要按全额报销花钱。</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2480,12 +2585,12 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>齐鲁明确收不回，美团险确认人民医院可赔</t>
+          <t>美团险已确认可赔、比例待书面</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>暂留市北区人民医院。留痕：保险认这家医院；赛主任每周查房谁来、哪天来。发热、伤口渗液、外固定松动、剧痛、脚趾发绀，立刻回三甲急诊。</t>
+          <t>暂留市北区人民医院。要书面比例、保单号。发热、伤口、外固定异常立刻回三甲急诊。</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -2565,7 +2670,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>用发票重做台账。8月15日「约7万」和8月16日「不到3.5万」冲突，对外前必须核死。</t>
+          <t>用发票分清：用工方垫付现金 3 万，费用口径确认 4 万。对外只报对上票的数。</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2878,7 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>8/16口径累计不到35000，须对账单</t>
+          <t>费用口径确认 4 万，须对账单</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2906,11 @@
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>医保范围内用药，保险可赔、比例待定</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr"/>
@@ -2829,7 +2938,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>24小时一对一，合同+发票；按责比例报，不是全额。家属自己陪护无票</t>
+          <t>24小时一对一，合同+发票；按责比例报</t>
         </is>
       </c>
     </row>
@@ -2899,31 +3008,31 @@
       <c r="A12" s="4" t="inlineStr"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>雇主垫付（通话口径）</t>
+          <t>用工方垫付现金</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>待核是否属实</t>
+          <t>已付待写收据</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>货主?</t>
+          <t>乔刘记商贸/刘孝春</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>收据</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>8/15口述，未与3.5万口径对上</t>
+          <t>写明垫付不是借款、不是了结、不冲抵欠薪</t>
         </is>
       </c>
     </row>
@@ -2931,7 +3040,7 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>未结工钱（通话口径）</t>
+          <t>未结工钱</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
@@ -2944,18 +3053,18 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>货主</t>
+          <t>刘孝春</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>欠条</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>不要直接冲抵事故赔偿</t>
+          <t>另写一张，不乘 30%，不和 3 万垫付混</t>
         </is>
       </c>
     </row>
@@ -2963,7 +3072,7 @@
       <c r="A14" s="4" t="inlineStr"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>责任方已付</t>
+          <t>责任方已付（美团侧）</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -2971,12 +3080,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>未付</t>
+          <t>待拉群</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>骑手/美团</t>
+          <t>骑手/平台险</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2987,7 +3096,7 @@
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>截至8/16通话称一分未付</t>
+          <t>保单和限额待骑手拉群</t>
         </is>
       </c>
     </row>
@@ -3076,17 +3185,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>家属</t>
+          <t>律师</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>取齐鲁 33 床补打出院记录交人民医院办住院号；同时去一楼收费窗口办结余原路退；问王主任：保险不认二甲能否收回齐鲁</t>
+          <t>看监控和车辆材料后，书面确定走简易还是一般；同意任何责任比例前先看完</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>空窗最危险；补打件不用单独盖章；能回齐鲁就回</t>
+          <t>家属确认程序由律师定。有驾驶证则无证风险下降，无牌风险仍要评估</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3101,17 +3210,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>家属+骑手</t>
+          <t>家属+刘孝春</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>加 1866 开头微信，催保险客服书面答复：市北区人民医院（抚顺路院区）认不认、赔付比例、要不要认定书才能垫</t>
+          <t>立刻写 3 万现金收据：垫付医疗费，不是借款，不是了结事故，不冲抵欠薪，不代美团赔。欠薪约 5000 另写一张</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>骑手 8/17 下午只说打了客服还没回信，不能当成已经确认</t>
+          <t>不写性质，事后可能被说成借款或已赔完。不必等法院先确认法律关系</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3131,12 +3240,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>下载并保存三份 CT 报告、齐鲁手术记录、费用明细和发票</t>
+          <t>用发票分清「垫付 3 万」和「费用口径 4 万」；催陈师傅认定书预计出具日</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>这是目前最硬的伤情和花费证据</t>
+          <t>两套数不能同时对外</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3151,17 +3260,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>家属+赛主任+交警</t>
+          <t>家属+骑手</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>医院资质公对公留痕：交警电话可给赛主任，口径必须是交警原话</t>
+          <t>拉群确认：保险公司名称、保单号、报案号、限额、人民医院书面赔付比例</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>不代扮交警，不换号</t>
+          <t>已确认可以赔、比例待定；平台是美团，承保公司未定</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3176,17 +3285,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>交警</t>
+          <t>家属</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>本周约骑手面谈；要平台保险名称、保单/工号、理赔窗口和是否须认定书</t>
+          <t>办成人民医院住院号；保存三份 CT、追手术记录和植入物清单</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>钱主要来自平台险，不是骑手现金</t>
+          <t>钢钉根数、后续方案、残级还没有正式文件</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3206,12 +3315,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>面谈只谈已发生费用和后续流程，不谈残级、不签总包死价</t>
+          <t>护士站请本院合作一对一 24 小时护工（合同+发票）；面谈不谈残级、不签总包</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>残还评不了，现在锁死会吃亏</t>
+          <t>护理费要票；残还评不了</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3220,55 +3329,19 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>家属</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>护士站请本院合作一对一 24 小时护工（合同+发票）；胡继刚办完住院号、拉群、约交警后回上海上班</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>现在不能自理，12 小时夜里没人；家属自己陪护的工资报不了，护工发票才能按责报护理费</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>家属+岳父</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>内部固定刘孝春角色：车是他的、活是他的、无劳动合同；先收微信转账、现场证人，不发律师函，不签与刘了结</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>他可能分担己方份额和车主过错，但不能替美团骑手补差额，两笔账不能混</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>未完成</t>
-        </is>
-      </c>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
@@ -3291,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3325,7 +3398,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>我们接受「看视频、任何一方都不是全责」这一事实前提。</t>
+          <t>我们接受「看视频、任何一方都不是全责」。认定书尚未出具。</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3410,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>掉头先右再左，是因为哈尔滨路水果市场 1 号门斜坡护栏开口借道，不是随意变道。双方口述都往上走。请结合监控和现场勘查写进认定书。我们仍不争全责。</t>
+          <t>地点请写：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。掉头先右再左是护栏开口借道，不是随意变道。</t>
         </is>
       </c>
     </row>
@@ -3349,31 +3422,31 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>请协助本周见到骑手，并请对方当场确认美团/保险公司联系人。</t>
+          <t>请协助见到骑手并拉保险进群。简易或一般程序我们听律师看完监控再定。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>对交警</t>
+          <t>对骑手/平台</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>就医医院请书面或通话留痕：默认三甲；若暂留二甲，是否影响保险审核。</t>
+          <t>先看病、先垫付已发生医疗费，态度摆正，拉群不打游击电话。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>对交警</t>
+          <t>对骑手/平台</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>简易程序可以谈，但要先问清保险能否在该责任比例下正常赔。</t>
+          <t>请拉群确认保险公司名称、保单号、限额和书面赔付比例。人民医院可以赔，比例还没书面。</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3458,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>先看病、先垫付已发生医疗费，态度摆正，拉群不打游击电话。</t>
+          <t>不接受「等认定书之前什么都不做」。认定书管责任，不管伤者今天能不能住院。</t>
         </is>
       </c>
     </row>
@@ -3397,31 +3470,31 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>请平台和保险进群。8 月 17 日你说已打客服、加 1866 微信，现在要书面结果：人民医院认不认、赔付比例。</t>
+          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>对骑手/平台</t>
+          <t>对医院</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>不接受「等认定书之前什么都不做」。认定书管责任，不管伤者今天能不能住院。</t>
+          <t>请先协助：补打的 33 床出院记录交给人民医院办住院号；结余去一楼收费窗口原路退。若美团险不认二甲，请王主任协助退回齐鲁连续治疗。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>对骑手/平台</t>
+          <t>对医院</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
+          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运、开具发票。</t>
         </is>
       </c>
     </row>
@@ -3433,31 +3506,31 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>请先协助：补打的 33 床出院记录交给人民医院办住院号；结余去一楼收费窗口原路退。若美团险不认二甲，请王主任协助退回齐鲁连续治疗。</t>
+          <t>请出具诊断证明、手术名称、预计住院和康复周期。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>对医院</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>需要转院请书面告知原因、是否联合体、结算规则，并协助专业转运、开具发票。</t>
+          <t>请书面确认：市北区人民医院（抚顺路院区）可赔，赔付比例是多少，医保范围内用药如何核，要不要认定书才能垫付。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>对医院</t>
+          <t>对保险公司</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>请出具诊断证明、手术名称、预计住院和康复周期。</t>
+          <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3542,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>请确认：山东大学齐鲁医院（青岛）已发生费用、市北区人民医院（抚顺路院区）后续费用，是否都属于可赔医院。请用医院全称核对。</t>
+          <t>请告知理赔需要的材料清单、是否必须先有责任认定书才能垫付医疗费。</t>
         </is>
       </c>
     </row>
@@ -3481,31 +3554,31 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
+          <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>对保险公司</t>
+          <t>绝对不要说</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>请告知理赔需要的材料清单、是否必须先有责任认定书才能垫付医疗费。</t>
+          <t>不要再说「对方全责」——交警视频已经排除。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>对保险公司</t>
+          <t>绝对不要说</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
+          <t>不要对外说「已经几级伤残」。</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3590,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>不要再说「对方全责」——交警视频已经排除。</t>
+          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3602,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>不要对外说「已经几级伤残」。</t>
+          <t>不要为了走一般程序去赌全责。驾驶人有证，但无牌风险仍在，程序由律师定。</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3614,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>不要把右足骨刺、退变说成这次撞出来的跟骨粉碎骨折。</t>
+          <t>不要把 3 万垫付说成借款或事故已经了结。</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3626,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+          <t>不要去人社局报工伤。未签劳动合同，不具备工伤认定条件。</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3638,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>不要无发票的现金开支事后补口。</t>
+          <t>不要等法院先确认雇佣关系才去写收据、要欠薪——现在就能写。</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3650,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
+          <t>不要无发票的现金开支事后补口。</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3662,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>不要把医保结算说成美团险已经确认。</t>
+          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3674,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>不要说伤者已经进入康复期。</t>
+          <t>不要把医保结算说成美团险已经确认。</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3686,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
+          <t>不要说伤者已经进入康复期。</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3698,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3710,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>不要把刘孝春写成工伤单位去人社局；退休未签合同，工伤这条很窄。</t>
+          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3722,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>不要对外说叉车。涉事是货运三轮。</t>
+          <t>不要把刘孝春写成工伤单位去人社局；未签劳动合同，工伤已排除。</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3734,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
+          <t>不要对外说叉车。涉事是货运三轮。</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3746,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
+          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3758,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
+          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3770,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3782,24 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
+          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>绝对不要说</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>不要写成给孙总干活。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B35"/>
+  <autoFilter ref="A1:B36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -3729,7 +3814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3740,7 +3825,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>交警视频已排除全责。程序选择不要赌全责。</t>
+          <t>认定书尚未出具。简易或一般由律师看监控后定。</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3854,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>干活在青岛市市北区批发市场一带。8 月 18 日口述更细：哈尔滨路水果市场门口、1 号门出口斜坡、护栏开口处，还没到红绿灯大路口。录音里还有红枫路汽车市场、福生批发市场、服装批发市场斜坡红绿灯等叫法，可能指同一片，地址以交警文书为准。不要写成纯市场内部事故，也不要写成叉车事故。</t>
+          <t>青岛市市北区抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。护栏开口借道掉头。录音里的红枫路汽车市场、福生、服装批发市场斜坡等停用。用户一条写「抚松路」按抚顺路统一。地址仍以认定书为准。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>材料里写抚顺路市政道路，不要写成市场内部</t>
+          <t>对外用抚顺路与哈尔滨路交叉口，以认定书为准</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3888,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>三轮车交警认定为机动车，未悬挂正规机动车号牌（只有抚顺路批发市场内部牌，无青岛市摩托车/机动车号牌；家属记得 2588，交警不认可）；车况旧：转向灯失灵，8 月 18 日口述大灯也坏，掉头未有效提示后方；掉头动作：先向上/向右借道再大弧度左拐。8 月 18 日家属解释是 1 号门斜坡护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
+          <t>三轮车：货运三轮，交警口头认定为机动车；只有抚顺路批发市场内部牌，无青岛市机动车号牌；左转向灯失灵（另有口述大灯也坏）；掉头先向右再向左大弧度。家属解释是护栏开口借道，待认定书；掉头动作：先向上/向右借道再大弧度左拐。8 月 18 日家属解释是 1 号门斜坡护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3825,7 +3910,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>要求主责，保底同等</t>
+          <t>要求主责，保底同等；待认定书</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3922,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>监控可排除任何一方全责。可能结果只有两种：双方同等责任；或三轮次责、外卖主责。交警称无论简易、一般程序还是法院，看了视频都不会超出该范围。8 月 18 日内部说的「骑手 70%、刘孝春 30%、驾驶人 0 责」是讨论意见，不是认定书。</t>
+          <t>书面认定书尚未出具。监控可排除任何一方全责。可能同等，或外卖主责、三轮次责。双方过错描述待认定书。简易或一般程序由律师看监控和车辆材料后确定，家属不自己拍板。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>停止使用「对方全责」</t>
+          <t>认定书未出；停止使用「对方全责」</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3944,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>可谈，但先确认平台保险能赔</t>
+          <t>可以谈，是否走由律师定</t>
         </is>
       </c>
     </row>
@@ -3871,85 +3956,102 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>鉴定约一个多月；无牌/可能无证要处罚</t>
+          <t>无青岛市号牌仍有风险；驾驶人有证，无证风险下降</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>除非保险拒赔或对方不谈，否则不主动升级</t>
+          <t>律师看完监控再选，家属不拍板</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>交警赔钱</t>
+          <t>驾驶资格</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>只出认定书，不参与金额</t>
+          <t>家属确认具备驾驶资格证书</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>金额找保险和法院，别逼交警</t>
+          <t>内部留证，不要主动交给一般程序扩查</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>刘孝春身份</t>
+          <t>交警赔钱</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，当时没有签劳动合同。</t>
+          <t>只出认定书，不参与金额</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>车主/接受劳务方，不是工伤单位</t>
+          <t>金额找保险和法院，别逼交警</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>不替美团补</t>
+          <t>刘孝春身份</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>刘孝春没有法定义务承担「美团小姑娘责任范围内赔不够、她本人又没钱」的那一块。那是骑手和美团平台险的债，不能让老板去替她补。</t>
+          <t>乔刘记商贸负责人刘孝春。伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，雇佣关系，未签劳动合同。</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>骑手责任范围内的缺口仍找平台险和骑手</t>
+          <t>乔刘记商贸；雇佣无合同；工伤排除</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>不替美团补</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>刘孝春没有法定义务承担「美团小姑娘责任范围内赔不够、她本人又没钱」的那一块。那是骑手和美团平台险的债，不能让老板去替她补。</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>骑手责任范围内的缺口仍找平台险和骑手</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>可主张己方份</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>认定书扣掉的己方份额（同等大约 50%，次责大约 30%）以及因车主过错、提供不合格车辆产生的相应责任，可以向刘孝春主张分担。这是「三轮这一方内部怎么分」，不是「替美团赔剩余」。</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>无牌+灯坏交人使用，车主有过错线索；先留证据不发函</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>无牌+灯坏交人使用；3万垫付先写收据</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -4021,17 +4123,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>按实际未付工钱，8/15 口述约 5000 元，须微信或证人核。</t>
+          <t>按实际未付工钱，口述约 5000 元，须另写欠条/微信确认。</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100% 由刘孝春付。这是欠薪，不乘 30%，不和事故赔偿冲抵。</t>
+          <t>100% 由刘孝春付。这是欠薪，不乘 30%，不和 3 万垫付、4 万医疗口径冲抵。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>不要拿欠薪去抵医疗费后说事故两清。</t>
+          <t>不要拿欠薪去抵 3 万垫付后说事故两清。</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4560,7 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>工伤待遇、社保补缴——退休未签合同，这条基本走不通。</t>
+          <t>工伤待遇、社保补缴——未签劳动合同，家属确认不具备工伤认定条件。</t>
         </is>
       </c>
     </row>

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -7,47 +7,50 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤情鉴定" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤残情况" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外伤与退变对照" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转院报销" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法律关系提醒" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="办理顺序" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤情鉴定" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤残情况" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外伤与退变对照" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转院报销" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法律关系提醒" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'伤情鉴定'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤残情况'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'转院报销'!$A$1:$C$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'转院报销'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'费用台账'!$A$2:$H$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'费用台账'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'沟通口径卡'!$A$1:$B$36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'沟通口径卡'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'责任与程序'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'责任与程序'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'刘孝春分担清单'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'法律关系提醒'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'法律关系提醒'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'待补充信息'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'录音来源'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'办理顺序'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'办理顺序'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤情鉴定'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'伤残情况'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'外伤与退变对照'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'转院报销'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'转院报销'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'费用台账'!$A$2:$H$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'费用台账'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'72小时待办'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'沟通口径卡'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'沟通口径卡'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'责任与程序'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'责任与程序'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'刘孝春分担清单'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'法律关系提醒'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'法律关系提醒'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'待补充信息'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'录音来源'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +81,25 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <color rgb="001F2A37"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00A63D2F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00B57A2A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="000B2F5B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -90,19 +110,8 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="001F2A37"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="001F2A37"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="000B2F5B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -150,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -158,22 +167,40 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,178 +566,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>齐鲁医院云影像 · 谁受伤、伤了什么（2026-08-17 核对）</t>
+          <t>现阶段不谈总赔偿数额。先固定监控和用工证据，取得书面认定，确认保险与医院资格，核清费用；鉴定后再算。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>检查号</t>
+          <t>缓急</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>项目 / 科室</t>
+          <t>时限</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>影像所见（报告原文）</t>
+          <t>事项</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>影像诊断（报告原文）</t>
+          <t>谁来办</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>本次事故？</t>
+          <t>怎么办理</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>完成标志</t>
         </is>
       </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>10008056847</t>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>贯穿禁止</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>右小腿CT平扫（薄层）＋骨三维成像
-急诊 · 急诊骨科 · 已审核</t>
+          <t>从现在到评残结束</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>右侧胫骨远端、腓骨近端骨质不连续，断端移位，踝关节对位不良，胫距关节间隙增宽。距骨内缘、外踝下方见小骨片影。右小腿、踝关节软组织肿胀。</t>
+          <t>不谈总赔偿数额</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>右侧胫骨远端、腓骨近端骨折，并踝关节半脱位
-右距骨内缘、外踝撕脱性骨折
-右小腿、踝关节软组织肿胀</t>
+          <t>全体对外场合（骑手、保险、刘孝春、交警）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>是，计入本次</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>10008056848</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>右足CT平扫（薄层）＋骨三维成像
-急诊 · 急诊骨科 · 已审核</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>右足诸关节在位，组成骨结构完整，边缘见骨质增生，跟骨见骨刺影，第一跖骨头见囊状低密度影，边缘硬化。</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>右足退行性变、跟骨骨刺
-右第一跖骨头囊变</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>否，退变/陈旧，不计入评残</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
+          <t>对骑手、刘孝春、保险只谈已发生发票、住院号、拉群、认定书进度。有人问「一共要多少」：答「费用还在发生，等认定书和治疗稳定后再按票算」。3 万垫付收据写明不是了结。内部测算数字不要发到群里。</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>所有书面沟通都没有总包数字；没有签了结协议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>紧急</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>本周，可并行</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>固定监控证据</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚 → 市北区交警陈师傅</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>微信或当面问四件事并请他回复留痕：①事故编号；②监控是否已调取、保存到何时；③家属或律师何时可查看、能否复制；④书面认定书预计哪天出具。不要只靠手机偷拍交警屏幕。能拿到复制件最好；拿不到至少要「已调取+允许查看」的微信回执。</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>事故编号 + 监控调取/查看回执（微信截图即可）写进台账。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>10008059257</t>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>紧急</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>右踝关节CT平扫（薄层）＋骨三维成像
-住院 · 手足与显微重建外科 · 已审核</t>
+          <t>本周，可并行</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>右踝关节骨折内外固定术后复查，内外固定在位，位线可。周围软组织肿胀，密度增高。</t>
+          <t>固定用工证据</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>右踝关节骨折内外固定术后复查</t>
+          <t>胡继刚 + 刘孝春</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>是，计入本次</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>患者：胡** / 男 / 64岁　　医院：山东大学齐鲁医院（青岛）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>报告页注明：本报告仅供临床医生参考，不作任何证明。 这是影像诊断，不是伤残鉴定。</t>
+          <t>当天做三张纸：①3 万现金收据，写「垫付医疗费，不是借款，不是一次性了结交通事故，不冲抵未结工钱，不代美团赔偿」；②未结工钱约 5000 另写欠条/微信确认，不乘责任比例；③保存派活微信、内部牌照片、转向灯损坏照片、当天卸货事实。营业执照或微信抬头能要则要。不要去人社局报工伤。</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>收据原件、欠条/微信确认、派活和车辆照片已拍照备份。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>紧急</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>本周，可并行</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>确认医院资格并办住院号</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>家属 → 人民医院入院处 / 齐鲁出院处</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>先办齐鲁出院结算和 33 床出院记录，再办人民医院住院号。向保险书面确认：市北区人民医院（抚顺路院区）是否可赔、赔付比例、医保范围内用药如何核。口径是二级以上公立、医保范围内用药可以；比例未书面确定前不要按全额报销花钱。出院前索取住院费用清单、诊断证明、出院小结。发热、伤口、外固定异常立刻回三甲急诊。</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>住院号办成；保险对医院资格有书面或群内文字答复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>紧急</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>本周，可并行</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>确认保险（承保公司、保单、比例）</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>家属 + 骑手拉群</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>骑手必须拉群：骑手、站点、保险客服、家属。群里书面要：保险公司全称、保单号、报案号、限额、人民医院书面赔付比例、要不要认定书才能垫付医疗费、理赔材料清单。不要只打电话。超 3 天无保险对接人，才触发律师函，现在不先发。</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>四方微信群建立；保单号/报案号和书面比例（或「待书面」的催告记录）在群里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>紧急</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>本周起持续</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>核清全部费用</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>家属（医院窗口 + 护工公司 + 刘孝春收据）</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>用发票做台账，分清：刘孝春垫付现金 3 万是一笔；费用口径 4 万是累计还是另一笔。逐项贴票：齐鲁手术/CT、人民医院、药品、护工合同+发票（本院合作一对一 24 小时）、救护车 160 元。医保已报金额单独记，避免重复报。记录 13 的 8000 元、蒋玉年不是本案。无票现金先不要对外报。</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Excel 费用台账能对上发票；对外只报对上票的一个数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1–2 周</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>取得书面责任认定</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚催陈师傅；签字前律师看</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>本周先要「预计出具日」。收到认定书先核对：地点是否写抚顺路与哈尔滨路交叉口、双方身份、过错描述、责任比例。不服有复核期，不要当场情绪化拒签，先拍照发给律师。认定书不管金额，不要逼交警写赔多少。简易或一般程序由律师看完监控再定，家属不自己拍板。</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>认定书原件在手，复印件/照片已备份；路名和责任比例已记下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>急</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>看完监控后、签程序前</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>律师确定简易或一般程序</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>处理交通事故的本地律师（岳父场外即可）；家属不拍板</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>律师看监控复制件或到场查看、看内部牌和灯坏情况后，书面或微信明确「走简易」或「走一般」。同意任何责任比例之前必须看完。现在不请诉讼律师当面谈、不先发律师函。</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>律师对程序有明确意见；家属按该意见回复交警。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>治疗期间持续，不挡本周急事</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>补现场与护栏证据</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚补拍；以认定书为准</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>补拍护栏开口、路口方向、内部牌。3D 示范动画留作待用，等交警原视频再做写实，本次不重做。对外地点统一用：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>现场照片已存；认定书正式路名已核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>后</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>病情稳定、鉴定条件成熟（常见伤后约 3 个月，以鉴定机构书面要求为准）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>再计算交通事故赔偿和用工责任请求</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>家属 + 律师；司法鉴定机构</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>治疗终结后做道路交通事故伤残鉴定（人体损伤致残程度分级），用途写清交通事故，右足骨刺不送评，不要走人社局工伤标准。鉴定后才计算：①对骑手/美团平台险的交通事故赔偿（按认定书比例）；②对刘孝春的雇员受害（民法典 1192）和车主过错（1209），只切己方缺口里与其过错相当的部分，不替美团补约 70%。未结工钱始终 100% 由刘付。谈不拢再起诉。</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>鉴定意见出具后，按票+残级+责任比例列出请求清单，再进入调解或起诉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>贯穿禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>不要现在谈总赔偿数额、总包、一次性了结，也不要报残级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>不要把内部测算（残疾赔偿金基数、70%/30%）说给骑手或刘孝春当报价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>不要去人社局报工伤；用工责任按雇员受害和车主过错另走。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>不要签任何写着「一次了结、以后不再主张」的纸，包括微信里口头两清。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>3 万垫付收据必须写清：垫付医疗费，不是借款，不是了结。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>本案现阶段不应急于谈一个总赔偿数额。应先固定监控和用工证据、取得书面责任认定、确认保险与医院资格、核清全部费用，再在病情稳定及鉴定条件成熟后计算交通事故赔偿，以及可能的雇员受害/车主过错请求。本案未签劳动合同，不具备工伤认定条件，不要去人社局报工伤。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
-  <mergeCells count="3">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:F7"/>
+  <autoFilter ref="A1:G21"/>
+  <mergeCells count="8">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -718,6 +1059,542 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>30%是己方缺口不是刘的固定比例。未结工钱100%由刘付，其余进总损失后再切。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>现在能否主张</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>计算口径</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>刘孝春怎么担</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>不要搞错</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>未结工钱（欠薪）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>可以现在就要</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>按实际未付工钱，口述约 5000 元，须另写欠条/微信确认。</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100% 由刘孝春付。这是欠薪，不乘 30%，不和 3 万垫付、4 万医疗口径冲抵。</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>不要拿欠薪去抵 3 万垫付后说事故两清。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>医疗费</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>有票就进台账</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>住院、手术、检查、药品、后续门诊，发票减医保已报（按保险和法院口径）。</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>进入 L，刘分担缺口 G 中与其过错相当的部分。</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>美团 70% 仍找平台险，不让刘替骑手出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>后续治疗费</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>评残前先记账，取内固定后再结</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>医嘱或鉴定意见载明的二次手术、拆外固定、康复必要费用。</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>同上，进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>不要现在把尚未发生的二次手术一次性包死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>护理费（陪护费）</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>应当主张</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>医院合作一对一 24 小时合同+发票；出院后仍不能自理的，按医嘱天数和当地护工价。青岛约 300–350 元/天。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>应当分担缺口里的护理费，不是把全部护工费甩给刘。家属自己陪护无票的，很难按上海工资认。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>一对多、微信私拉、无发票，刘和保险都可以不认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>住院伙食补助费</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>应当主张</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>住院天数 × 青岛国家机关工作人员出差伙食补助标准。</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>没有住院天数就不要编。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>营养费</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>有医嘱再主张</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>医嘱写加强营养或鉴定支持的天数 × 当地标准。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>没有医嘱不要按骨折吓人程度口头加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>交通费</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>有票就主张</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>救护车 160 元；家属合理往返（胡继刚上海—青岛按必要次数）。</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>旅游、探亲顺便的车票不要混进去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>住宿费</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>有票且必要才主张</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>外地家属因处理事故、陪护产生的合理住宿。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>长期住酒店替代护工，容易被砍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>误工费（伤者本人）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>能证明收入才主张</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>只算胡某。64 岁已退休，须证明实际在给刘干活有收入（微信、证人、市场行情）。误工天数看出院医嘱或鉴定休息期。</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>误工费若成立，刘分担的是缺口里这一项，不是按儿子上海工资赔，也不是把胡某后半生工资全包。</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>证明不了实际收入，误工费可能为 0。胡继刚的工资不是误工费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>残疾赔偿金</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>评残后才有</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>青岛口径内部用 71703 元/年 × 16 年 × 残级系数（十级 0.1，九级 0.2）。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>评残后进入 L，刘仍只切 30% 缺口里与其过错相当的部分。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>现在不要对外报残级，也不要让刘现在按十级锁死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>残疾辅助器具费</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>有医嘱或鉴定再主张</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>拐杖、轮椅等必要器具。</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>高消费器材没有医嘱不要报。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>被扶养人生活费</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>评残后看有没有法定被扶养人</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>须评残且有胡某依法扶养、无劳动能力又无生活来源的人。成年儿子胡继刚一般不算。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>若成立，进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>不要把全家生活费写成被扶养人生活费。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>精神损害抚慰金</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>评残或起诉时主张</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>按伤情和当地法院尺度。美团平台险常常不赔这一项。</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>保险不赔的部分，可向有过错的侵权人主张；刘作为车主/接受劳务过错方，可能分担己方缺口里的相应部分，不是替骑手把精神抚慰金全包。</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>不要以为刘必须把保险除外的精神抚慰金全部补上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>鉴定费</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>评残时发生</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>道路交通事故伤残鉴定费，发票。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口；有的判决由败诉方负担，以判决为准。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>不要网上计算器代替鉴定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>个人物品损失</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>有凭证再主张</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>衣服、眼镜、手机等因事故损坏。</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>进 L 后切缺口。</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>三轮车是刘的，车损不是胡某向刘索赔的项目；车损由刘自行向美团侧按责主张。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>不应承担</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>美团骑手责任范围内（约 70%）赔不够的部分——仍是骑手和平台险的债。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>胡继刚回上海少拿的工资、请护工之外自己陪护的「误工」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>无合同、无发票的现金护工，以及一对多护工。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>跟骨骨刺、退变等与本次事故无关的治疗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>把刘孝春的三轮车损算成胡某的损失向刘要钱。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>工伤待遇、社保补缴——未签劳动合同，家属确认不具备工伤认定条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>现在就按十级、九级向刘要残疾赔偿金。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>总损失 L（下列可计入项目之和）→ 美团/平台险先赔约 70%L → 己方缺口 G≈30%L → 刘孝春赔 G×其过错系数 k，胡某自负 G×(1−k)。k 不是 100%，也不要对外报一个数；无牌+灯坏交人上路、当天派活，主张时把 k 往高处谈，但不能写成刘把 30% 全部包圆。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E28"/>
+  <mergeCells count="9">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -760,10 +1637,10 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>工伤已经排除：未签劳动合同，不具备工伤认定条件。不要去人社局。</t>
         </is>
@@ -780,10 +1657,10 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>3 万元现金立刻写收据：垫付医疗费，不是借款，不是一次性了结交通事故，不冲抵欠薪，不代美团赔偿。</t>
         </is>
@@ -800,10 +1677,10 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>4 万元和 3 万元用发票分清后再对外报一个数。</t>
         </is>
@@ -819,7 +1696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -897,27 +1774,27 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>护栏与地点</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>家属确认：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口；护栏开口借道</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>认定书正式路名、现场图、护栏开口照片</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>认定书 / 胡继刚补拍</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -951,27 +1828,27 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>胡某驾驶资格</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>家属确认具备驾驶资格证书</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>内部留驾驶证复印件。不要主动交给一般程序扩查</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>胡继刚内部</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -1005,27 +1882,27 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>交警程序</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>监控已调、排除全责、两车已扣；认定书尚未出具</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>预计出具时间；律师看完监控再选简易或一般；认定书原件</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>陈师傅 + 律师</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>急</t>
         </is>
@@ -1059,27 +1936,27 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>姓名核对</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>对接人胡继刚；齐鲁转写 33 床胡志远；用工老板口述刘孝春（转写刘小春）；有人问过孙总被否认</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>身份证、病历首页、微信实名，对外材料只用证件姓名</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>胡继刚</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>急</t>
         </is>
@@ -1113,27 +1990,27 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>医院手续</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>齐鲁手术 8/15；人已到人民医院；保险侧确认二甲可赔、比例待定</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>住院号；书面赔付比例；手术记录和植入物清单（钢钉根数）</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>入院处 / 保险书面 / 病案室</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>急</t>
         </is>
@@ -1167,27 +2044,27 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>美团骑手</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>女骑手、美团平台、二轮</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>姓名、电话、站点名称；拉群确认保险公司和保单</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>骑手拉群</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>急</t>
         </is>
@@ -1203,7 +2080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1270,22 +2147,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>2｜轻弦办公椅园区快闪洽谈</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>07:59</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>与事故无关，见附录</t>
         </is>
@@ -1314,22 +2191,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>4｜与骑手赔偿责任通话</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>03:19</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>骑手要等认定书；家属要求拉群、不满未探望</t>
         </is>
@@ -1358,22 +2235,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>6｜红枫路交警沟通</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>责任范围、简易/一般、保险、医院级别</t>
         </is>
@@ -1402,22 +2279,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>8｜交警：二甲入院与执行风险</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>06:08</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>三甲默认、二甲不确定、骑手偿付弱</t>
         </is>
@@ -1446,22 +2323,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>10｜与赛主任转院沟通</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>03:27</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>联合体二甲惯例；交警电话公对公</t>
         </is>
@@ -1490,22 +2367,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>12｜请对方联系保险公司</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>00:39</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>让二轮女骑手联系保险；能赔才留人民医院</t>
         </is>
@@ -1534,22 +2411,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>14｜骑手侧保险报销确认</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>02:00</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>骑手称已打客服未回信；加微信 1866；地点有人叫福生批发市场</t>
         </is>
@@ -1578,22 +2455,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>16｜律师选择与费用（另一案）</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>仅作收费常识。九级、25–30 万、远洋工伤是另一案，不能套本案</t>
         </is>
@@ -1622,22 +2499,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>书面｜家属确认待确认事项</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>书面</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>认定书未出；抚顺路路口；有驾驶证；人民医院可赔比例待定；乔刘记商贸；垫付 3 万；费用口径 4 万；工伤排除；程序由律师定</t>
         </is>
@@ -1653,7 +2530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1696,10 +2573,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>合作：物业大堂快闪 + 企业内购；单椅成交返佣 100–200 元；可用椅子抵场地费。</t>
         </is>
@@ -1716,10 +2593,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>下一步：供方发资料；合作方下下周回沪后选 1–2 个园区试点。</t>
         </is>
@@ -1741,6 +2618,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>齐鲁医院云影像 · 谁受伤、伤了什么（2026-08-17 核对）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>检查号</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>项目 / 科室</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>影像所见（报告原文）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>影像诊断（报告原文）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>本次事故？</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>10008056847</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>右小腿CT平扫（薄层）＋骨三维成像
+急诊 · 急诊骨科 · 已审核</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>右侧胫骨远端、腓骨近端骨质不连续，断端移位，踝关节对位不良，胫距关节间隙增宽。距骨内缘、外踝下方见小骨片影。右小腿、踝关节软组织肿胀。</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>右侧胫骨远端、腓骨近端骨折，并踝关节半脱位
+右距骨内缘、外踝撕脱性骨折
+右小腿、踝关节软组织肿胀</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>是，计入本次</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>10008056848</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>右足CT平扫（薄层）＋骨三维成像
+急诊 · 急诊骨科 · 已审核</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>右足诸关节在位，组成骨结构完整，边缘见骨质增生，跟骨见骨刺影，第一跖骨头见囊状低密度影，边缘硬化。</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>右足退行性变、跟骨骨刺
+右第一跖骨头囊变</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>否，退变/陈旧，不计入评残</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>10008059257</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>右踝关节CT平扫（薄层）＋骨三维成像
+住院 · 手足与显微重建外科 · 已审核</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>右踝关节骨折内外固定术后复查，内外固定在位，位线可。周围软组织肿胀，密度增高。</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>右踝关节骨折内外固定术后复查</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>是，计入本次</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>患者：胡** / 男 / 64岁　　医院：山东大学齐鲁医院（青岛）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>报告页注明：本报告仅供临床医生参考，不作任何证明。 这是影像诊断，不是伤残鉴定。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <mergeCells count="3">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1791,17 +2852,17 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>现在有没有残级</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>尚未做伤残鉴定。云影像三份 CT 是影像诊断，不是伤残鉴定书，不能当残级用。</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>对外禁止说「已经几级」</t>
         </is>
@@ -1825,17 +2886,17 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>用哪套标准</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>道路交通事故人身损害评残，实务中多用《人体损伤致残程度分级》（两院三部 2017）。不要用工伤标准去套交通事故，也不要按网上计算器先报一个级数给对方。</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>交通事故用人体损伤致残程度分级，不要套工伤</t>
         </is>
@@ -1859,24 +2920,24 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>现在能否报价</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>现在不能、也不应对外报「几级伤残」。等级取决于日后功能，不取决于急诊 CT 有多吓人。</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>面谈不谈残级、不签总包死价</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>评残前材料清单</t>
         </is>
@@ -1894,15 +2955,15 @@
       <c r="C11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>后续每次复查都留报告（是否骨愈合、是否感染、踝关节活动度）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1916,15 +2977,15 @@
       <c r="C13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>鉴定机构须合法，报告用途写清「道路交通事故」</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1953,7 +3014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2015,18 +3076,18 @@
       </c>
     </row>
     <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CT：非本次外伤</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>• 右足组成骨结构完整，诸关节在位，未见本次外伤性骨折
 • 右足退行性变、跟骨骨刺、第一跖骨头囊变：属退变/陈旧改变，一般不计入本次交通事故伤残</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>不要写成跟骨粉碎骨折</t>
         </is>
@@ -2050,17 +3111,17 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>通话里说「腓骨下段/小腿外侧骨折」</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>急诊小腿 CT 写的是「腓骨近端」骨折，另有「外踝撕脱性骨折」（外踝属腓骨远端）。两处都要记，不要只记一处。</t>
         </is>
@@ -2084,17 +3145,17 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>8 月 15 日部分通话说已出院回家</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>同日住院 CT 在手足与显微重建外科，证明当时仍在齐鲁医院住院术后复查，并未结束治疗。</t>
         </is>
@@ -2118,17 +3179,17 @@
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>地点有红枫路、哈尔滨路、福生批发市场、服装批发市场斜坡红绿灯等说法</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>家属确认：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。对外用这一条，仍以认定书为准。用户一条里写「抚松路」按抚顺路统一。</t>
         </is>
@@ -2152,17 +3213,17 @@
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>录音写成「胡志远」</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>家属对接人是儿子胡继刚。伤者写胡某。姓名以身份证、病历首页为准。</t>
         </is>
@@ -2186,17 +3247,17 @@
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>合集目录把 17 份拆成多起车祸/叉车/行人</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>记录 1、3–15、17 是同一起三轮×美团女骑手事故。记录 2 轻弦无关。记录 16 是另一案。</t>
         </is>
@@ -2220,17 +3281,17 @@
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>记录 13 出现蒋玉年、陈先建、26 床、8000 元</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>病区串台。本案只取 33 床补打出院记录、一楼原路退费。其他人和其他钱不要进台账。</t>
         </is>
@@ -2254,17 +3315,17 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>通话须改口</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>记录 17 说驾驶人 0 责、刘孝春把 30% 全包</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>内部设想。交警仍可能把无牌、灯坏、掉头记在三轮使用人胡某这一方。</t>
         </is>
@@ -2280,7 +3341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2336,17 +3397,17 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>怎么转出来的</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>院方口径是联合体、同一家医院、不影响质量。昨天沟通过两次没转成，父亲好说话才同意，今天上午才搬走。主治态度强硬，青岛这边没有上海那种关系。</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>父亲好说话才同意；主治强硬，不指望找关系留床</t>
         </is>
@@ -2370,17 +3431,17 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>两条报销</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>报销仍分两条：① 医保：公立二甲通常能结算；② 美团平台险：家属确认可以赔、比例待定，二级以上公立医院医保范围内用药可以。比例和限额仍要书面，不能当全额。</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>医保和美团险分开问</t>
         </is>
@@ -2404,17 +3465,17 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>结算规则</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>跨院必须先在上一院结算，才能办下一院入院。出院部和科室权责分离，只找出院部催科室留床没有用。证件、押金票据带到齐鲁办理窗口（通话提到 11 楼）。</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>带齐证件和押金票</t>
         </is>
@@ -2438,17 +3499,17 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>家属口径</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>家属确认人民医院可以赔、比例待定。向保险继续要书面：赔付比例、保单号、限额、要不要认定书才能垫付。医院全称：市北区人民医院（抚顺路院区）。</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>采用；向保险报医院全称</t>
         </is>
@@ -2472,17 +3533,17 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>今天目标</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>住院号办成；保险书面比例拿到手。可以暂留人民医院，但比例未定不要当全额报销。</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>手续打通 + 美团险确认二甲</t>
         </is>
@@ -2506,17 +3567,17 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>首选齐鲁</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>手术在齐鲁手足与显微重建外科做的，内外固定还在，术后只有两天，软组织仍肿。齐鲁是三甲，交警默认三甲，病历连续，出现伤口或外固定问题能找原手术组。这是医疗和理赔都最稳的选择。</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>赛主任态度强硬，床位周转考核，明确不愿让交通事故患者长期占床。昨天谈了两次才转出，父亲已经同意搬走。没有关系硬闯，成功率不高。所以是合法问一次能不能收回，不是闹回去。</t>
         </is>
@@ -2540,17 +3601,17 @@
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>不默认留二甲</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>市北区人民医院是公立二甲、联合体，环境清静，赛主任称可每周查房。但现在入院手续都没办成；美团险还没确认认不认；术后两天不是康复期。医保能报不能代替美团险确认。</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>先问美团险，先办入院号</t>
         </is>
@@ -2570,17 +3631,17 @@
       <c r="C17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>齐鲁能收回</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>回齐鲁。这是首选。不要再转第三次。</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -2596,17 +3657,17 @@
       <c r="C19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>美团险不认人民医院</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>不要继续住。请保险医务部门对接齐鲁或指定三甲。家属不自己满城找床。</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -2622,17 +3683,17 @@
       <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>对赛主任原话</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>赛主任，患者8月15日刚做完右踝内外固定，今天二甲入院手续还办不成。交警口径是交通事故尽量三甲。术后只有两天，不是康复期。请协助：要么尽快办完出院让二甲能入院，要么收回齐鲁本院连续治疗。我们按医院规则走，不闹、不装病。</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>不闹、不装病</t>
         </is>
@@ -2648,7 +3709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2727,7 +3788,7 @@
           <t>急诊右小腿CT（10008056847）</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr"/>
+      <c r="C3" s="14" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>已付待核</t>
@@ -2751,34 +3812,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>急诊右足CT（10008056848）</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>已付待核</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>待贴</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>齐鲁医院</t>
         </is>
@@ -2795,7 +3856,7 @@
           <t>住院右踝CT术后复查（10008059257）</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>已付待核</t>
@@ -2819,34 +3880,34 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>右踝骨折内外固定手术</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>已付待核</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>待贴</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>以手术记录为准</t>
         </is>
@@ -2859,7 +3920,7 @@
           <t>住院押金/预缴</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>已付待核</t>
@@ -2883,30 +3944,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>药品（院内）</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>已付待核</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>待贴</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>医保范围内用药，保险可赔、比例待定</t>
         </is>
@@ -2919,7 +3980,7 @@
           <t>护工费</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>已付待核</t>
@@ -2943,30 +4004,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>护理耗材（垫、便盆等）</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>已付待核</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>待贴</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2979,7 +4040,7 @@
           <t>转院救护车</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="14" t="n">
         <v>160</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3005,32 +4066,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>用工方垫付现金</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>已付待写收据</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>乔刘记商贸/刘孝春</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>收据</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>写明垫付不是借款、不是了结、不冲抵欠薪</t>
         </is>
@@ -3043,7 +4104,7 @@
           <t>未结工钱</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="14" t="n">
         <v>5000</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3069,44 +4130,44 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>责任方已付（美团侧）</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>待拉群</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>骑手/平台险</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>保单和限额待骑手拉群</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>合计（仅填写了数字的行）</t>
         </is>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="16">
         <f>SUM(C3:C14)</f>
         <v/>
       </c>
@@ -3129,7 +4190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3148,7 +4209,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>今天先打通出院入院，并向保险公司确认二甲。不谈残级。</t>
+          <t>本周紧急事项执行清单。不谈总赔偿数额、不谈残级。</t>
         </is>
       </c>
     </row>
@@ -3205,25 +4266,25 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>家属+刘孝春</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>立刻写 3 万现金收据：垫付医疗费，不是借款，不是了结事故，不冲抵欠薪，不代美团赔。欠薪约 5000 另写一张</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>不写性质，事后可能被说成借款或已赔完。不必等法院先确认法律关系</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -3255,25 +4316,25 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>家属+骑手</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>拉群确认：保险公司名称、保单号、报案号、限额、人民医院书面赔付比例</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>已确认可以赔、比例待定；平台是美团，承保公司未定</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -3305,25 +4366,25 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>护士站请本院合作一对一 24 小时护工（合同+发票）；面谈不谈残级、不签总包</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>护理费要票；残还评不了</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>未完成</t>
         </is>
@@ -3337,11 +4398,11 @@
       <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
@@ -3358,7 +4419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3403,12 +4464,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>对交警</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>地点请写：抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。掉头先右再左是护栏开口借道，不是随意变道。</t>
         </is>
@@ -3427,12 +4488,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>对骑手/平台</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>先看病、先垫付已发生医疗费，态度摆正，拉群不打游击电话。</t>
         </is>
@@ -3451,12 +4512,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>对骑手/平台</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>不接受「等认定书之前什么都不做」。认定书管责任，不管伤者今天能不能住院。</t>
         </is>
@@ -3470,17 +4531,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
+          <t>今天不谈总赔偿数额、不谈残级，不签一次性了结。费用还在发生，等认定书和治疗稳定后再按票算。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>对医院</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>请先协助：补打的 33 床出院记录交给人民医院办住院号；结余去一楼收费窗口原路退。若美团险不认二甲，请王主任协助退回齐鲁连续治疗。</t>
         </is>
@@ -3499,12 +4560,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>对医院</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>请出具诊断证明、手术名称、预计住院和康复周期。</t>
         </is>
@@ -3523,12 +4584,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>对保险公司</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>如果二甲不认，请贵司医务部门对接医院，协调转回三甲连续治疗。</t>
         </is>
@@ -3547,12 +4608,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>对保险公司</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>护理费：伤者目前不能下地、不能独自如厕，已请医院合作一对一 24 小时护工。请确认按发票、按责任比例核赔；家属误工不在伤者误工项里。</t>
         </is>
@@ -3571,14 +4632,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>不要对外说「已经几级伤残」。</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>不要现在谈一个总赔偿数额、不要对外说「已经几级伤残」。</t>
         </is>
       </c>
     </row>
@@ -3595,12 +4656,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>不要为了走一般程序去赌全责。驾驶人有证，但无牌风险仍在，程序由律师定。</t>
         </is>
@@ -3619,12 +4680,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>不要去人社局报工伤。未签劳动合同，不具备工伤认定条件。</t>
         </is>
@@ -3643,12 +4704,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>不要无发票的现金开支事后补口。</t>
         </is>
@@ -3667,12 +4728,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>不要把医保结算说成美团险已经确认。</t>
         </is>
@@ -3691,12 +4752,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
@@ -3715,12 +4776,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>不要把刘孝春写成工伤单位去人社局；未签劳动合同，工伤已排除。</t>
         </is>
@@ -3739,12 +4800,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
         </is>
@@ -3763,12 +4824,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
         </is>
@@ -3787,12 +4848,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>绝对不要说</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>不要写成给孙总干活。</t>
         </is>
@@ -3808,7 +4869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3864,17 +4925,17 @@
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>过程</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>以监控为准，不补充猜测</t>
         </is>
@@ -3898,17 +4959,17 @@
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>骑手过错</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>未与前车保持足够安全距离；处于后方、视野更清楚，有条件提前规避</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>要求主责，保底同等；待认定书</t>
         </is>
@@ -3932,17 +4993,17 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>简易程序</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>不审资质，快出认定书</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>可以谈，是否走由律师定</t>
         </is>
@@ -3966,17 +5027,17 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>驾驶资格</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>家属确认具备驾驶资格证书</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>内部留证，不要主动交给一般程序扩查</t>
         </is>
@@ -4000,17 +5061,17 @@
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>刘孝春身份</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>乔刘记商贸负责人刘孝春。伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，雇佣关系，未签劳动合同。</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>乔刘记商贸；雇佣无合同；工伤排除</t>
         </is>
@@ -4034,17 +5095,17 @@
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>可主张己方份</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>认定书扣掉的己方份额（同等大约 50%，次责大约 30%）以及因车主过错、提供不合格车辆产生的相应责任，可以向刘孝春主张分担。这是「三轮这一方内部怎么分」，不是「替美团赔剩余」。</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>无牌+灯坏交人使用；3万垫付先写收据</t>
         </is>
@@ -4058,540 +5119,4 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>30%是己方缺口不是刘的固定比例。未结工钱100%由刘付，其余进总损失后再切。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>现在能否主张</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>计算口径</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>刘孝春怎么担</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>不要搞错</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>未结工钱（欠薪）</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>可以现在就要</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>按实际未付工钱，口述约 5000 元，须另写欠条/微信确认。</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>100% 由刘孝春付。这是欠薪，不乘 30%，不和 3 万垫付、4 万医疗口径冲抵。</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>不要拿欠薪去抵 3 万垫付后说事故两清。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>医疗费</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>有票就进台账</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>住院、手术、检查、药品、后续门诊，发票减医保已报（按保险和法院口径）。</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>进入 L，刘分担缺口 G 中与其过错相当的部分。</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>美团 70% 仍找平台险，不让刘替骑手出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>后续治疗费</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>评残前先记账，取内固定后再结</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>医嘱或鉴定意见载明的二次手术、拆外固定、康复必要费用。</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>同上，进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>不要现在把尚未发生的二次手术一次性包死。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>护理费（陪护费）</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>应当主张</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>医院合作一对一 24 小时合同+发票；出院后仍不能自理的，按医嘱天数和当地护工价。青岛约 300–350 元/天。</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>应当分担缺口里的护理费，不是把全部护工费甩给刘。家属自己陪护无票的，很难按上海工资认。</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>一对多、微信私拉、无发票，刘和保险都可以不认。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>住院伙食补助费</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>应当主张</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>住院天数 × 青岛国家机关工作人员出差伙食补助标准。</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>没有住院天数就不要编。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>营养费</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>有医嘱再主张</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>医嘱写加强营养或鉴定支持的天数 × 当地标准。</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>没有医嘱不要按骨折吓人程度口头加。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>交通费</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>有票就主张</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>救护车 160 元；家属合理往返（胡继刚上海—青岛按必要次数）。</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>旅游、探亲顺便的车票不要混进去。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>住宿费</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>有票且必要才主张</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>外地家属因处理事故、陪护产生的合理住宿。</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>长期住酒店替代护工，容易被砍。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>误工费（伤者本人）</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>能证明收入才主张</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>只算胡某。64 岁已退休，须证明实际在给刘干活有收入（微信、证人、市场行情）。误工天数看出院医嘱或鉴定休息期。</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>误工费若成立，刘分担的是缺口里这一项，不是按儿子上海工资赔，也不是把胡某后半生工资全包。</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>证明不了实际收入，误工费可能为 0。胡继刚的工资不是误工费。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>残疾赔偿金</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>评残后才有</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>青岛口径内部用 71703 元/年 × 16 年 × 残级系数（十级 0.1，九级 0.2）。</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>评残后进入 L，刘仍只切 30% 缺口里与其过错相当的部分。</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>现在不要对外报残级，也不要让刘现在按十级锁死。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>残疾辅助器具费</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>有医嘱或鉴定再主张</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>拐杖、轮椅等必要器具。</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>高消费器材没有医嘱不要报。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>被扶养人生活费</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>评残后看有没有法定被扶养人</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>须评残且有胡某依法扶养、无劳动能力又无生活来源的人。成年儿子胡继刚一般不算。</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>若成立，进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>不要把全家生活费写成被扶养人生活费。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>精神损害抚慰金</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>评残或起诉时主张</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>按伤情和当地法院尺度。美团平台险常常不赔这一项。</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>保险不赔的部分，可向有过错的侵权人主张；刘作为车主/接受劳务过错方，可能分担己方缺口里的相应部分，不是替骑手把精神抚慰金全包。</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>不要以为刘必须把保险除外的精神抚慰金全部补上。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>鉴定费</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>评残时发生</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>道路交通事故伤残鉴定费，发票。</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口；有的判决由败诉方负担，以判决为准。</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>不要网上计算器代替鉴定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>个人物品损失</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>有凭证再主张</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>衣服、眼镜、手机等因事故损坏。</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>进 L 后切缺口。</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>三轮车是刘的，车损不是胡某向刘索赔的项目；车损由刘自行向美团侧按责主张。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>不应承担</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>美团骑手责任范围内（约 70%）赔不够的部分——仍是骑手和平台险的债。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>胡继刚回上海少拿的工资、请护工之外自己陪护的「误工」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>无合同、无发票的现金护工，以及一对多护工。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>跟骨骨刺、退变等与本次事故无关的治疗。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>把刘孝春的三轮车损算成胡某的损失向刘要钱。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>工伤待遇、社保补缴——未签劳动合同，家属确认不具备工伤认定条件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>现在就按十级、九级向刘要残疾赔偿金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总损失 L（下列可计入项目之和）→ 美团/平台险先赔约 70%L → 己方缺口 G≈30%L → 刘孝春赔 G×其过错系数 k，胡某自负 G×(1−k)。k 不是 100%，也不要对外报一个数；无牌+灯坏交人上路、当天派活，主张时把 k 往高处谈，但不能写成刘把 30% 全部包圆。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E28"/>
-  <mergeCells count="9">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A22:E22"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -8,49 +8,52 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="办理顺序" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤情鉴定" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤残情况" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外伤与退变对照" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转院报销" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法律关系提醒" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料核心" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤情鉴定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="伤残情况" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外伤与退变对照" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="转院报销" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用台账" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="72小时待办" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沟通口径卡" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任与程序" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="刘孝春分担清单" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法律关系提醒" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待补充信息" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="录音来源" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录轻弦洽谈" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'办理顺序'!$A$1:$G$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'办理顺序'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'伤情鉴定'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'伤残情况'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'转院报销'!$A$1:$C$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'转院报销'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'费用台账'!$A$2:$H$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'费用台账'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'72小时待办'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'沟通口径卡'!$A$1:$B$36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'沟通口径卡'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'责任与程序'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'责任与程序'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'刘孝春分担清单'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'法律关系提醒'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'法律关系提醒'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'待补充信息'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'录音来源'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'录音来源'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'附录轻弦洽谈'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'材料核心'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'材料核心'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'伤情鉴定'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'伤情鉴定'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'伤残情况'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'伤残情况'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'外伤与退变对照'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'转院报销'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'转院报销'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'费用台账'!$A$2:$H$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'费用台账'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'72小时待办'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'72小时待办'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'沟通口径卡'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'沟通口径卡'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'责任与程序'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'责任与程序'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'刘孝春分担清单'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'刘孝春分担清单'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'法律关系提醒'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'法律关系提醒'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'待补充信息'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'待补充信息'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'录音来源'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'录音来源'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'附录轻弦洽谈'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'附录轻弦洽谈'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1064,6 +1067,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>认定书尚未出具。简易或一般由律师看监控后定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>交警口径</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>家属对策</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>地点</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>青岛市市北区抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。护栏开口借道掉头。录音里的红枫路汽车市场、福生、服装批发市场斜坡等停用。用户一条写「抚松路」按抚顺路统一。地址仍以认定书为准。</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>对外用抚顺路与哈尔滨路交叉口，以认定书为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>过程</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>以监控为准，不补充猜测</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>三轮过错</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>三轮车：货运三轮，交警口头认定为机动车；只有抚顺路批发市场内部牌，无青岛市机动车号牌；左转向灯失灵（另有口述大灯也坏）；掉头先向右再向左大弧度。家属解释是护栏开口借道，待认定书；掉头动作：先向上/向右借道再大弧度左拐。8 月 18 日家属解释是 1 号门斜坡护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>承认监控里看得到的问题，不争口头全责</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>骑手过错</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>未与前车保持足够安全距离；处于后方、视野更清楚，有条件提前规避</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>要求主责，保底同等；待认定书</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>责任范围</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>书面认定书尚未出具。监控可排除任何一方全责。可能同等，或外卖主责、三轮次责。双方过错描述待认定书。简易或一般程序由律师看监控和车辆材料后确定，家属不自己拍板。</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>认定书未出；停止使用「对方全责」</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>简易程序</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>不审资质，快出认定书</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>可以谈，是否走由律师定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>一般程序</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>无青岛市号牌仍有风险；驾驶人有证，无证风险下降</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>律师看完监控再选，家属不拍板</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>驾驶资格</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>家属确认具备驾驶资格证书</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>内部留证，不要主动交给一般程序扩查</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>交警赔钱</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>只出认定书，不参与金额</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>金额找保险和法院，别逼交警</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>刘孝春身份</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>乔刘记商贸负责人刘孝春。伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，雇佣关系，未签劳动合同。</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>乔刘记商贸；雇佣无合同；工伤排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>不替美团补</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>刘孝春没有法定义务承担「美团小姑娘责任范围内赔不够、她本人又没钱」的那一块。那是骑手和美团平台险的债，不能让老板去替她补。</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>骑手责任范围内的缺口仍找平台险和骑手</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>可主张己方份</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>认定书扣掉的己方份额（同等大约 50%，次责大约 30%）以及因车主过错、提供不合格车辆产生的相应责任，可以向刘孝春主张分担。这是「三轮这一方内部怎么分」，不是「替美团赔剩余」。</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>无牌+灯坏交人使用；3万垫付先写收据</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1594,7 +1849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1696,7 +1951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2080,7 +2335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2530,7 +2785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2613,6 +2868,368 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>17 份转写去重：转院只三点，事故四条，立即八事。费用按 4 万元逐笔核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>怎么做 / 口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>转院三点</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>先完成原医院结算</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>齐鲁出院结算、33 床出院记录、押金原路退。跨院必须先结上一院，才能办人民医院入院。 完成：齐鲁出院手续办完，人民医院能收材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>转院三点</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>确认新医院能否正常入院</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>市北区人民医院（抚顺路院区）办住院号。医疗安全为先：手续卡住先问齐鲁能否收回，不要另找三甲碰运气。 完成：住院号办成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>转院三点</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>向实际承保公司书面确认二甲赔付资格和比例</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>骑手拉群报案。要保单号、书面比例。不依赖交警、医院或非经办人员的口头判断。家属确认可以赔、比例待定，不等于书面已到。 完成：书面或群内文字：认不认人民医院、比例多少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>事故四条</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>早期口述</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>伤者和家属早期口述事故、伤情、费用及「对方全责」看法。全责已被 8 月 17 日交警监控排除，早期口述不作对外口径。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>事故四条</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>与骑手通话</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>家属与骑手通话，确认书面责任认定尚未出具，并提出建立多方沟通群。</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>事故四条</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>交警口头分析（最关键）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>交警根据监控说明双方过错及简易/一般两种程序。书面认定书尚未出具。排除任何一方全责。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>事故四条</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>内部讨论</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>家属对车辆行驶路线、护栏影响、车辆归属和责任比例的内部讨论。护栏开口可解释掉头动作，不能据此争全责；「骑手 70%、用工方 30%」是内部设想，不是交警结论。</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>向交警确认书面事故认定书的进度，并索取事故编号、监控保存情况及简易/一般程序的书面说明。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚 → 陈师傅。口头排除全责不能当证据。没有编号和监控回执，等于还没固定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>本地交通事故律师（岳父场外）。驾驶人有证，无证风险下降；无青岛市号牌风险仍在。家属不自己拍板。现在不请诉讼律师当面谈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>向实际承保保险公司报案并取得书面答复，不再依赖交警、医院或非经办人员的口头判断。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>家属 + 骑手拉群。对方无交强险。大头在美团平台险。人民医院可以赔、比例待书面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>以医疗安全为先确定住院地点，补齐齐鲁医院出院结算、出院记录和市北区人民医院入院材料。</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>家属 → 齐鲁出院处 / 人民医院入院处。转院类录音大量重复，核心就是结算、入院、保险书面确认这三步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>立即建立费用台账，逐笔核清 4 万元金额。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>家属。家属确认费用口径 4 万。须用发票重核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>保存事故监控、全部病历、票据、转运材料及沟通记录原件和电子备份。</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>家属。原件和照片/扫描各一份。监控至少要调取回执。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为用工责任主张留证。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚 + 刘孝春。工伤认定条件目前不具备（未签劳动合同），不去人社局报工伤。这些材料用于雇员受害和车主过错。3 万收据、5000 欠条现在就写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>立即八事</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>待病情稳定并达到鉴定条件后，再由有资质机构进行伤残鉴定；不要根据录音中的推测提前确定等级或金额。</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>家属 + 鉴定机构（后）。现阶段不谈总赔偿数额。记录 16 的九级、25–30 万是另一案，不能套到本案。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D17"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2796,7 +3413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3014,7 +3631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3341,7 +3958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3540,7 +4157,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>住院号办成；保险书面比例拿到手。可以暂留人民医院，但比例未定不要当全额报销。</t>
+          <t>住院号办成；保险书面比例拿到手。转院录音只看三点：齐鲁先结算、人民医院能入院、承保公司书面确认二甲资格和比例。可以暂留人民医院，但比例未定不要当全额报销。</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3709,7 +4326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4190,7 +4807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4200,16 +4817,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>本周紧急事项执行清单。不谈总赔偿数额、不谈残级。</t>
+          <t>立即八事。转院录音只看三点。费用按 4 万元逐笔核。不谈总赔偿数额。</t>
         </is>
       </c>
     </row>
@@ -4240,23 +4857,23 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>律师</t>
+          <t>胡继刚 → 陈师傅</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>看监控和车辆材料后，书面确定走简易还是一般；同意任何责任比例前先看完</t>
+          <t>向交警确认书面事故认定书的进度，并索取事故编号、监控保存情况及简易/一般程序的书面说明。</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>家属确认程序由律师定。有驾驶证则无证风险下降，无牌风险仍要评估</t>
+          <t>口头排除全责不能当证据。没有编号和监控回执，等于还没固定。</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -4265,23 +4882,23 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>家属+刘孝春</t>
+          <t>本地交通事故律师（岳父场外）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>立刻写 3 万现金收据：垫付医疗费，不是借款，不是了结事故，不冲抵欠薪，不代美团赔。欠薪约 5000 另写一张</t>
+          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>不写性质，事后可能被说成借款或已赔完。不必等法院先确认法律关系</t>
+          <t>驾驶人有证，无证风险下降；无青岛市号牌风险仍在。家属不自己拍板。现在不请诉讼律师当面谈。</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4290,23 +4907,23 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>家属</t>
+          <t>家属 + 骑手拉群</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>用发票分清「垫付 3 万」和「费用口径 4 万」；催陈师傅认定书预计出具日</t>
+          <t>向实际承保保险公司报案并取得书面答复，不再依赖交警、医院或非经办人员的口头判断。</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>两套数不能同时对外</t>
+          <t>对方无交强险。大头在美团平台险。人民医院可以赔、比例待书面。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -4315,23 +4932,23 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>家属+骑手</t>
+          <t>家属 → 齐鲁出院处 / 人民医院入院处</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>拉群确认：保险公司名称、保单号、报案号、限额、人民医院书面赔付比例</t>
+          <t>以医疗安全为先确定住院地点，补齐齐鲁医院出院结算、出院记录和市北区人民医院入院材料。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>已确认可以赔、比例待定；平台是美团，承保公司未定</t>
+          <t>转院类录音大量重复，核心就是结算、入院、保险书面确认这三步。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4340,7 +4957,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -4351,12 +4968,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>办成人民医院住院号；保存三份 CT、追手术记录和植入物清单</t>
+          <t>立即建立费用台账，逐笔核清 4 万元金额。</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>钢钉根数、后续方案、残级还没有正式文件</t>
+          <t>家属确认费用口径 4 万。须用发票重核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4365,7 +4982,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
@@ -4376,12 +4993,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>护士站请本院合作一对一 24 小时护工（合同+发票）；面谈不谈残级、不签总包</t>
+          <t>保存事故监控、全部病历、票据、转运材料及沟通记录原件和电子备份。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>护理费要票；残还评不了</t>
+          <t>原件和照片/扫描各一份。监控至少要调取回执。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4390,19 +5007,55 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>胡继刚 + 刘孝春</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为用工责任主张留证。</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>工伤认定条件目前不具备（未签劳动合同），不去人社局报工伤。这些材料用于雇员受害和车主过错。3 万收据、5000 欠条现在就写。</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>家属 + 鉴定机构（后）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>待病情稳定并达到鉴定条件后，再由有资质机构进行伤残鉴定；不要根据录音中的推测提前确定等级或金额。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>现阶段不谈总赔偿数额。记录 16 的九级、25–30 万是另一案，不能套到本案。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
@@ -4419,7 +5072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4867,256 +5520,4 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>认定书尚未出具。简易或一般由律师看监控后定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>交警口径</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>家属对策</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>地点</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>青岛市市北区抚顺路批发市场，抚顺路与哈尔滨路交叉口，主要在抚顺路路口。护栏开口借道掉头。录音里的红枫路汽车市场、福生、服装批发市场斜坡等停用。用户一条写「抚松路」按抚顺路统一。地址仍以认定书为准。</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>对外用抚顺路与哈尔滨路交叉口，以认定书为准</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>过程</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>以监控为准，不补充猜测</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>三轮过错</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>三轮车：货运三轮，交警口头认定为机动车；只有抚顺路批发市场内部牌，无青岛市机动车号牌；左转向灯失灵（另有口述大灯也坏）；掉头先向右再向左大弧度。家属解释是护栏开口借道，待认定书；掉头动作：先向上/向右借道再大弧度左拐。8 月 18 日家属解释是 1 号门斜坡护栏开口需要先借道；交警仍可能把该动作写成未有效提示后方</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>承认监控里看得到的问题，不争口头全责</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>骑手过错</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>未与前车保持足够安全距离；处于后方、视野更清楚，有条件提前规避</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>要求主责，保底同等；待认定书</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>责任范围</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>书面认定书尚未出具。监控可排除任何一方全责。可能同等，或外卖主责、三轮次责。双方过错描述待认定书。简易或一般程序由律师看监控和车辆材料后确定，家属不自己拍板。</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>认定书未出；停止使用「对方全责」</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>简易程序</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>不审资质，快出认定书</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>可以谈，是否走由律师定</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>一般程序</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>无青岛市号牌仍有风险；驾驶人有证，无证风险下降</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>律师看完监控再选，家属不拍板</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>驾驶资格</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>家属确认具备驾驶资格证书</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>内部留证，不要主动交给一般程序扩查</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>交警赔钱</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>只出认定书，不参与金额</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>金额找保险和法院，别逼交警</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>刘孝春身份</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>乔刘记商贸负责人刘孝春。伤者当时的雇佣老板，三轮车实际所有人或管理人。64 岁胡某已退休，雇佣关系，未签劳动合同。</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>乔刘记商贸；雇佣无合同；工伤排除</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>不替美团补</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>刘孝春没有法定义务承担「美团小姑娘责任范围内赔不够、她本人又没钱」的那一块。那是骑手和美团平台险的债，不能让老板去替她补。</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>骑手责任范围内的缺口仍找平台险和骑手</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>可主张己方份</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>认定书扣掉的己方份额（同等大约 50%，次责大约 30%）以及因车主过错、提供不合格车辆产生的相应责任，可以向刘孝春主张分担。这是「三轮这一方内部怎么分」，不是「替美团赔剩余」。</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>无牌+灯坏交人使用；3万垫付先写收据</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -34,7 +34,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'伤残情况'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'外伤与退变对照'!$A$1:$C$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'外伤与退变对照'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'转院报销'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'转院报销'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'转院报销'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'费用台账'!$A$2:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'费用台账'!$1:$2</definedName>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
+          <t>在同意任何责任比例或程序选择前，让处理交通事故的本地律师查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>家属。家属确认费用口径 4 万。须用发票重核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
+          <t>家属。费用口径就是 4 万。用发票逐笔核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为用工责任主张留证。</t>
+          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为可能的工伤或用工责任主张留证。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>胡继刚 + 刘孝春。工伤认定条件目前不具备（未签劳动合同），不去人社局报工伤。这些材料用于雇员受害和车主过错。3 万收据、5000 欠条现在就写。</t>
+          <t>胡继刚 + 刘孝春。留证现在做。未签劳动合同，工伤认定条件目前不具备，不去人社局；用工责任按雇员受害和车主过错主张。3 万收据、5000 欠条现在就写。</t>
         </is>
       </c>
     </row>
@@ -3964,360 +3964,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人已到人民医院，齐鲁出院未办。医保能报 ≠ 美团险能报。</t>
+          <t>转院录音大量重复。核心只三点：原医院结算、新医院入院、承保公司书面确认二甲。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>事项</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>目前事实</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>怎么处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>当前卡住</t>
-        </is>
+          <t>怎么做 / 完成标志</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 家属确认：市北区人民医院费用可以赔，比例待定。口径：二级以上公立医院、医保范围内用药可以。人已到人民医院（公立二甲）。书面比例、保单号、住院号仍要盯。认定书尚未出具。</t>
+          <t>先完成原医院结算</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>要书面比例和住院号；可以暂留人民医院</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>怎么转出来的</t>
-        </is>
+          <t>齐鲁出院结算、33 床出院记录、押金原路退。跨院必须先结上一院，才能办人民医院入院。 完成：齐鲁出院手续办完，人民医院能收材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>院方口径是联合体、同一家医院、不影响质量。昨天沟通过两次没转成，父亲好说话才同意，今天上午才搬走。主治态度强硬，青岛这边没有上海那种关系。</t>
+          <t>确认新医院能否正常入院</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>父亲好说话才同意；主治强硬，不指望找关系留床</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+          <t>市北区人民医院（抚顺路院区）办住院号。医疗安全为先：手续卡住先问齐鲁能否收回，不要另找三甲碰运气。 完成：住院号办成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>向实际承保公司书面确认二甲赔付资格和比例</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>骑手拉群报案。要保单号、书面比例。不依赖交警、医院或非经办人员的口头判断。家属确认可以赔、比例待定，不等于书面已到。 完成：书面或群内文字：认不认人民医院、比例多少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>补</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>结算铁律</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>跨院必须先在上一院结算，才能办下一院入院。出院部和科室权责分离，只找出院部催科室留床没有用。证件、押金票据带到齐鲁办理窗口（通话提到 11 楼）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>补</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>找哪家保险</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>咨询人说「认定单上一定有保险公司电话」。本案对方是外卖电动车，没有交强险、商业三者险。认定书上未必印着人保/平安。要找的是美团平台险，问交警、骑手、站点，不要只在认定单上找传统车险公司。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>补</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>家属口径</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>家属确认人民医院可以赔、比例待定。向保险继续要书面：赔付比例、保单号、限额、要不要认定书才能垫付。医院全称：市北区人民医院（抚顺路院区）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>补</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>不是康复期</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>不要把现在当成康复期。8 月 15 日术后 CT 仍写软组织肿胀、内外固定刚做完，到 17 日只过了两天。朋友说「已经康复期就别折腾」与影像时间轴不符。</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>术后两天，软组织仍肿，不能按康复期处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>两条报销</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>报销仍分两条：① 医保：公立二甲通常能结算；② 美团平台险：家属确认可以赔、比例待定，二级以上公立医院医保范围内用药可以。比例和限额仍要书面，不能当全额。</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>医保和美团险分开问</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>找哪家保险</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>咨询人说「认定单上一定有保险公司电话」。本案对方是外卖电动车，没有交强险、商业三者险。认定书上未必印着人保/平安。要找的是美团平台险，问交警、骑手、站点，不要只在认定单上找传统车险公司。</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>问交警/骑手/站点要美团平台险，不在认定单上找交强险</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>结算规则</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>跨院必须先在上一院结算，才能办下一院入院。出院部和科室权责分离，只找出院部催科室留床没有用。证件、押金票据带到齐鲁办理窗口（通话提到 11 楼）。</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>带齐证件和押金票</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>朋友怎么说</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>8 月 17 日 12:57 咨询：对方称公立二甲及以上一般在保险报销范围内，民营和一级社区医院通常不认；还让把医院全称发给他核对。对方自己只是骨裂、没住院，不能当美团保单条款。</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>仅参考，不能当保单</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+    </row>
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>家属口径</t>
+          <t>禁</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>家属确认人民医院可以赔、比例待定。向保险继续要书面：赔付比例、保单号、限额、要不要认定书才能垫付。医院全称：市北区人民医院（抚顺路院区）。</t>
+          <t>不要另找三甲</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>采用；向保险报医院全称</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>别的三甲</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
           <t>不要另找别的三甲碰运气。齐鲁是山大直属附属医院，床位本就紧；全国三甲都考床位周转，病情未到「必须三甲抢救」时，别人也难收长期占床。</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>不另找山大体系外三甲碰运气</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>今天目标</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>住院号办成；保险书面比例拿到手。转院录音只看三点：齐鲁先结算、人民医院能入院、承保公司书面确认二甲资格和比例。可以暂留人民医院，但比例未定不要当全额报销。</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>手续打通 + 美团险确认二甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>医院怎么选</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>家属确认人民医院（公立二甲）费用可以赔，比例待定。二级以上公立医院、医保范围内用药可以。不必再为「二甲能不能报」来回搬人。比例书面未到之前，不要按全额报销花钱。</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>不另找三甲；不默认留二甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>首选齐鲁</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>手术在齐鲁手足与显微重建外科做的，内外固定还在，术后只有两天，软组织仍肿。齐鲁是三甲，交警默认三甲，病历连续，出现伤口或外固定问题能找原手术组。这是医疗和理赔都最稳的选择。</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>赛主任态度强硬，床位周转考核，明确不愿让交通事故患者长期占床。昨天谈了两次才转出，父亲已经同意搬走。没有关系硬闯，成功率不高。所以是合法问一次能不能收回，不是闹回去。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>不另找三甲</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>其他三甲同样考床位周转，不收刚做完手术、还要住一个月的占床。新医院不掌握术中情况，外固定再搬一次有风险，又要重新结算入院。只有齐鲁拒收且美团险不认人民医院时，才由保险协调下一家三甲。</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>只有保险书面指定才动</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>不默认留二甲</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>市北区人民医院是公立二甲、联合体，环境清静，赛主任称可每周查房。但现在入院手续都没办成；美团险还没确认认不认；术后两天不是康复期。医保能报不能代替美团险确认。</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>先问美团险，先办入院号</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>今天先做</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>办齐鲁出院结算，结束没有住院号的空窗。同时问赛主任：术后两天、外固定在、交警要求三甲、二甲还办不了入院，能否收回本院。同时问美团险：市北区人民医院（抚顺路院区）后续费用认不认。</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>齐鲁能收回</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>回齐鲁。这是首选。不要再转第三次。</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>美团险已确认可赔、比例待书面</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>暂留市北区人民医院。要书面比例、保单号。发热、伤口、外固定异常立刻回三甲急诊。</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>美团险不认人民医院</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>不要继续住。请保险医务部门对接齐鲁或指定三甲。家属不自己满城找床。</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>齐鲁拒收且保险也不认二甲、保险又协调不出三甲</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>这才考虑其他三甲，而且要保险书面指定，不要自己去碰。</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>对赛主任原话</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>赛主任，患者8月15日刚做完右踝内外固定，今天二甲入院手续还办不成。交警口径是交通事故尽量三甲。术后只有两天，不是康复期。请协助：要么尽快办完出院让二甲能入院，要么收回齐鲁本院连续治疗。我们按医院规则走，不闹、不装病。</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>不闹、不装病</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C22"/>
+  <autoFilter ref="A1:C10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -4893,7 +4703,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
+          <t>在同意任何责任比例或程序选择前，让处理交通事故的本地律师查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -4973,7 +4783,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>家属确认费用口径 4 万。须用发票重核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
+          <t>费用口径就是 4 万。用发票逐笔核，并与刘孝春垫付现金 3 万分清。不能再对外报 3.5 万或 7 万。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5018,12 +4828,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为用工责任主张留证。</t>
+          <t>核实伤者与用工方关系、车辆归属、工资结算和事故当日工作任务，为可能的工伤或用工责任主张留证。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>工伤认定条件目前不具备（未签劳动合同），不去人社局报工伤。这些材料用于雇员受害和车主过错。3 万收据、5000 欠条现在就写。</t>
+          <t>留证现在做。未签劳动合同，工伤认定条件目前不具备，不去人社局；用工责任按雇员受害和车主过错主张。3 万收据、5000 欠条现在就写。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_伤情伤残与行动表_20260817.xlsx
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>向实际承保公司书面确认二甲赔付资格和比例</t>
+          <t>向实际承保公司书面确认二甲医院的赔付资格和比例</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>伤者和家属早期口述事故、伤情、费用及「对方全责」看法。全责已被 8 月 17 日交警监控排除，早期口述不作对外口径。</t>
+          <t>伤者和家属早期口述事故、伤情、费用及「对方全责」看法。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+          <t>全责已排除，早期口述不作对外口径。</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+          <t>认定书尚未出具，先拉群。</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>交警根据监控说明双方过错及简易/一般两种程序。书面认定书尚未出具。排除任何一方全责。</t>
+          <t>最关键的交警口头分析，说明监控所见、双方过错及两种程序。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+          <t>书面认定书尚未出具。</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>家属对车辆行驶路线、护栏影响、车辆归属和责任比例的内部讨论。护栏开口可解释掉头动作，不能据此争全责；「骑手 70%、用工方 30%」是内部设想，不是交警结论。</t>
+          <t>家属对车辆行驶路线、护栏影响、车辆归属和责任比例的内部讨论。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早期全责不作对外口径；认定书未出；70/30 是内部设想</t>
+          <t>护栏可解释动作，不能据此争全责。</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>向实际承保公司书面确认二甲赔付资格和比例</t>
+          <t>向实际承保公司书面确认二甲医院的赔付资格和比例</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
